--- a/data/all_data_processed.xlsx
+++ b/data/all_data_processed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bob\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/972ffe9a7646a9ef/Documents/soft_sensor_based_on_pH_for_real_time_monitoring_of_mRNA_medicines_production/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F0AD12-A292-4A24-AE48-6D33FF644DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{D4F0AD12-A292-4A24-AE48-6D33FF644DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1601B6DF-B6F5-455C-97D3-19A1C4BC8920}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{114A7320-CEF1-4C40-AA85-5A8FF16848B1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{114A7320-CEF1-4C40-AA85-5A8FF16848B1}"/>
   </bookViews>
   <sheets>
     <sheet name="egfphepes" sheetId="4" r:id="rId1"/>
@@ -488,9 +488,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6AF59E-2EBB-4E7A-B460-53C5D38EA5B0}">
   <dimension ref="A1:L306"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="16.21875" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -528,7 +533,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -566,7 +571,7 @@
         <v>9.5299283450000001</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0.5</v>
       </c>
@@ -583,7 +588,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -600,7 +605,7 @@
       <c r="F4" s="1"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1.5</v>
       </c>
@@ -617,7 +622,7 @@
       <c r="F5" s="1"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -634,7 +639,7 @@
       <c r="F6" s="1"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2.5</v>
       </c>
@@ -651,7 +656,7 @@
       <c r="F7" s="1"/>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -668,7 +673,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3.5</v>
       </c>
@@ -685,7 +690,7 @@
       <c r="F9" s="1"/>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>4</v>
       </c>
@@ -723,7 +728,7 @@
         <v>9.2105496529999993</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>4.5</v>
       </c>
@@ -740,7 +745,7 @@
       <c r="F11" s="1"/>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5</v>
       </c>
@@ -757,7 +762,7 @@
       <c r="F12" s="1"/>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>5.5</v>
       </c>
@@ -774,7 +779,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>6</v>
       </c>
@@ -791,7 +796,7 @@
       <c r="F14" s="1"/>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>6.5</v>
       </c>
@@ -808,7 +813,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>7</v>
       </c>
@@ -825,7 +830,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>7.5</v>
       </c>
@@ -842,7 +847,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -880,7 +885,7 @@
         <v>8.0098989829999994</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>8.5</v>
       </c>
@@ -897,7 +902,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>9</v>
       </c>
@@ -914,7 +919,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>9.5</v>
       </c>
@@ -931,7 +936,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="3"/>
     </row>
-    <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>10</v>
       </c>
@@ -948,7 +953,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="3"/>
     </row>
-    <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>10.5</v>
       </c>
@@ -965,7 +970,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="3"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>11</v>
       </c>
@@ -982,7 +987,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>11.5</v>
       </c>
@@ -999,7 +1004,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="3"/>
     </row>
-    <row r="26" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>12</v>
       </c>
@@ -1016,7 +1021,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="3"/>
     </row>
-    <row r="27" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>12.5</v>
       </c>
@@ -1033,7 +1038,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="3"/>
     </row>
-    <row r="28" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>13</v>
       </c>
@@ -1071,7 +1076,7 @@
         <v>9.0072363430000006</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>13.5</v>
       </c>
@@ -1088,7 +1093,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="3"/>
     </row>
-    <row r="30" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>14</v>
       </c>
@@ -1105,7 +1110,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="3"/>
     </row>
-    <row r="31" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>14.5</v>
       </c>
@@ -1122,7 +1127,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>15</v>
       </c>
@@ -1139,7 +1144,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="3"/>
     </row>
-    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>15.5</v>
       </c>
@@ -1156,7 +1161,7 @@
       <c r="F33" s="1"/>
       <c r="G33" s="3"/>
     </row>
-    <row r="34" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>16</v>
       </c>
@@ -1173,7 +1178,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="3"/>
     </row>
-    <row r="35" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>16.5</v>
       </c>
@@ -1190,7 +1195,7 @@
       <c r="F35" s="1"/>
       <c r="G35" s="3"/>
     </row>
-    <row r="36" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>17</v>
       </c>
@@ -1207,7 +1212,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="3"/>
     </row>
-    <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>17.5</v>
       </c>
@@ -1224,7 +1229,7 @@
       <c r="F37" s="1"/>
       <c r="G37" s="3"/>
     </row>
-    <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>18</v>
       </c>
@@ -1262,7 +1267,7 @@
         <v>7.9024662980000002</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>18.5</v>
       </c>
@@ -1279,7 +1284,7 @@
       <c r="F39" s="1"/>
       <c r="G39" s="3"/>
     </row>
-    <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>19</v>
       </c>
@@ -1296,7 +1301,7 @@
       <c r="F40" s="1"/>
       <c r="G40" s="3"/>
     </row>
-    <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>19.5</v>
       </c>
@@ -1313,7 +1318,7 @@
       <c r="F41" s="1"/>
       <c r="G41" s="3"/>
     </row>
-    <row r="42" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>20</v>
       </c>
@@ -1330,7 +1335,7 @@
       <c r="F42" s="1"/>
       <c r="G42" s="3"/>
     </row>
-    <row r="43" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>20.5</v>
       </c>
@@ -1347,7 +1352,7 @@
       <c r="F43" s="1"/>
       <c r="G43" s="3"/>
     </row>
-    <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>21</v>
       </c>
@@ -1364,7 +1369,7 @@
       <c r="F44" s="1"/>
       <c r="G44" s="3"/>
     </row>
-    <row r="45" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>21.5</v>
       </c>
@@ -1381,7 +1386,7 @@
       <c r="F45" s="1"/>
       <c r="G45" s="3"/>
     </row>
-    <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>22</v>
       </c>
@@ -1398,7 +1403,7 @@
       <c r="F46" s="1"/>
       <c r="G46" s="3"/>
     </row>
-    <row r="47" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>22.5</v>
       </c>
@@ -1415,7 +1420,7 @@
       <c r="F47" s="1"/>
       <c r="G47" s="3"/>
     </row>
-    <row r="48" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>23</v>
       </c>
@@ -1453,7 +1458,7 @@
         <v>7.6629595180000001</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>23.5</v>
       </c>
@@ -1470,7 +1475,7 @@
       <c r="F49" s="1"/>
       <c r="G49" s="3"/>
     </row>
-    <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>24</v>
       </c>
@@ -1487,7 +1492,7 @@
       <c r="F50" s="1"/>
       <c r="G50" s="3"/>
     </row>
-    <row r="51" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>24.5</v>
       </c>
@@ -1504,7 +1509,7 @@
       <c r="F51" s="1"/>
       <c r="G51" s="3"/>
     </row>
-    <row r="52" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>25</v>
       </c>
@@ -1521,7 +1526,7 @@
       <c r="F52" s="1"/>
       <c r="G52" s="3"/>
     </row>
-    <row r="53" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>25.5</v>
       </c>
@@ -1538,7 +1543,7 @@
       <c r="F53" s="1"/>
       <c r="G53" s="3"/>
     </row>
-    <row r="54" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>26</v>
       </c>
@@ -1555,7 +1560,7 @@
       <c r="F54" s="1"/>
       <c r="G54" s="3"/>
     </row>
-    <row r="55" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>26.5</v>
       </c>
@@ -1572,7 +1577,7 @@
       <c r="F55" s="1"/>
       <c r="G55" s="3"/>
     </row>
-    <row r="56" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>27</v>
       </c>
@@ -1589,7 +1594,7 @@
       <c r="F56" s="1"/>
       <c r="G56" s="3"/>
     </row>
-    <row r="57" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>27.5</v>
       </c>
@@ -1606,7 +1611,7 @@
       <c r="F57" s="1"/>
       <c r="G57" s="3"/>
     </row>
-    <row r="58" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>28</v>
       </c>
@@ -1623,7 +1628,7 @@
       <c r="F58" s="1"/>
       <c r="G58" s="3"/>
     </row>
-    <row r="59" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>28.5</v>
       </c>
@@ -1640,7 +1645,7 @@
       <c r="F59" s="1"/>
       <c r="G59" s="3"/>
     </row>
-    <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>29</v>
       </c>
@@ -1657,7 +1662,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="3"/>
     </row>
-    <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>29.5</v>
       </c>
@@ -1674,7 +1679,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="3"/>
     </row>
-    <row r="62" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>30</v>
       </c>
@@ -1691,7 +1696,7 @@
       <c r="F62" s="1"/>
       <c r="G62" s="3"/>
     </row>
-    <row r="63" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>30.5</v>
       </c>
@@ -1708,7 +1713,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="3"/>
     </row>
-    <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>31</v>
       </c>
@@ -1746,7 +1751,7 @@
         <v>6.7930266379999997</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>31.5</v>
       </c>
@@ -1763,7 +1768,7 @@
       <c r="F65" s="1"/>
       <c r="G65" s="3"/>
     </row>
-    <row r="66" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>32</v>
       </c>
@@ -1780,7 +1785,7 @@
       <c r="F66" s="1"/>
       <c r="G66" s="3"/>
     </row>
-    <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>32.5</v>
       </c>
@@ -1797,7 +1802,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="3"/>
     </row>
-    <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>33</v>
       </c>
@@ -1814,7 +1819,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="3"/>
     </row>
-    <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>33.5</v>
       </c>
@@ -1831,7 +1836,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="3"/>
     </row>
-    <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>34</v>
       </c>
@@ -1848,7 +1853,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="3"/>
     </row>
-    <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>34.5</v>
       </c>
@@ -1865,7 +1870,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="3"/>
     </row>
-    <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>35</v>
       </c>
@@ -1882,7 +1887,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="3"/>
     </row>
-    <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>35.5</v>
       </c>
@@ -1899,7 +1904,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="3"/>
     </row>
-    <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>36</v>
       </c>
@@ -1916,7 +1921,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="3"/>
     </row>
-    <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>36.5</v>
       </c>
@@ -1933,7 +1938,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="3"/>
     </row>
-    <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>37</v>
       </c>
@@ -1950,7 +1955,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="3"/>
     </row>
-    <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>37.5</v>
       </c>
@@ -1967,7 +1972,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="3"/>
     </row>
-    <row r="78" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>38</v>
       </c>
@@ -1984,7 +1989,7 @@
       <c r="F78" s="1"/>
       <c r="G78" s="3"/>
     </row>
-    <row r="79" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>38.5</v>
       </c>
@@ -2001,7 +2006,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="3"/>
     </row>
-    <row r="80" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>39</v>
       </c>
@@ -2018,7 +2023,7 @@
       <c r="F80" s="1"/>
       <c r="G80" s="3"/>
     </row>
-    <row r="81" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>39.5</v>
       </c>
@@ -2035,7 +2040,7 @@
       <c r="F81" s="1"/>
       <c r="G81" s="3"/>
     </row>
-    <row r="82" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>40</v>
       </c>
@@ -2052,7 +2057,7 @@
       <c r="F82" s="1"/>
       <c r="G82" s="3"/>
     </row>
-    <row r="83" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>40.5</v>
       </c>
@@ -2069,7 +2074,7 @@
       <c r="F83" s="1"/>
       <c r="G83" s="3"/>
     </row>
-    <row r="84" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>41</v>
       </c>
@@ -2086,7 +2091,7 @@
       <c r="F84" s="1"/>
       <c r="G84" s="3"/>
     </row>
-    <row r="85" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>41.5</v>
       </c>
@@ -2103,7 +2108,7 @@
       <c r="F85" s="1"/>
       <c r="G85" s="3"/>
     </row>
-    <row r="86" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>42</v>
       </c>
@@ -2120,7 +2125,7 @@
       <c r="F86" s="1"/>
       <c r="G86" s="3"/>
     </row>
-    <row r="87" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>42.5</v>
       </c>
@@ -2137,7 +2142,7 @@
       <c r="F87" s="1"/>
       <c r="G87" s="3"/>
     </row>
-    <row r="88" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>43</v>
       </c>
@@ -2175,7 +2180,7 @@
         <v>6.1708864080000003</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>43.5</v>
       </c>
@@ -2192,7 +2197,7 @@
       <c r="F89" s="1"/>
       <c r="G89" s="3"/>
     </row>
-    <row r="90" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>44</v>
       </c>
@@ -2209,7 +2214,7 @@
       <c r="F90" s="1"/>
       <c r="G90" s="3"/>
     </row>
-    <row r="91" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>44.5</v>
       </c>
@@ -2226,7 +2231,7 @@
       <c r="F91" s="1"/>
       <c r="G91" s="3"/>
     </row>
-    <row r="92" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45</v>
       </c>
@@ -2243,7 +2248,7 @@
       <c r="F92" s="1"/>
       <c r="G92" s="3"/>
     </row>
-    <row r="93" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45.5</v>
       </c>
@@ -2260,7 +2265,7 @@
       <c r="F93" s="1"/>
       <c r="G93" s="3"/>
     </row>
-    <row r="94" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46</v>
       </c>
@@ -2277,7 +2282,7 @@
       <c r="F94" s="1"/>
       <c r="G94" s="3"/>
     </row>
-    <row r="95" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46.5</v>
       </c>
@@ -2294,7 +2299,7 @@
       <c r="F95" s="1"/>
       <c r="G95" s="3"/>
     </row>
-    <row r="96" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>47</v>
       </c>
@@ -2311,7 +2316,7 @@
       <c r="F96" s="1"/>
       <c r="G96" s="3"/>
     </row>
-    <row r="97" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>47.5</v>
       </c>
@@ -2328,7 +2333,7 @@
       <c r="F97" s="1"/>
       <c r="G97" s="3"/>
     </row>
-    <row r="98" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>48</v>
       </c>
@@ -2345,7 +2350,7 @@
       <c r="F98" s="1"/>
       <c r="G98" s="3"/>
     </row>
-    <row r="99" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>48.5</v>
       </c>
@@ -2362,7 +2367,7 @@
       <c r="F99" s="1"/>
       <c r="G99" s="3"/>
     </row>
-    <row r="100" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>49</v>
       </c>
@@ -2379,7 +2384,7 @@
       <c r="F100" s="1"/>
       <c r="G100" s="3"/>
     </row>
-    <row r="101" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>49.5</v>
       </c>
@@ -2396,7 +2401,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="3"/>
     </row>
-    <row r="102" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>50</v>
       </c>
@@ -2413,7 +2418,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="3"/>
     </row>
-    <row r="103" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>50.5</v>
       </c>
@@ -2430,7 +2435,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="3"/>
     </row>
-    <row r="104" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>51</v>
       </c>
@@ -2447,7 +2452,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="3"/>
     </row>
-    <row r="105" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>51.5</v>
       </c>
@@ -2464,7 +2469,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="3"/>
     </row>
-    <row r="106" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>52</v>
       </c>
@@ -2481,7 +2486,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="3"/>
     </row>
-    <row r="107" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>52.5</v>
       </c>
@@ -2498,7 +2503,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="3"/>
     </row>
-    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>53</v>
       </c>
@@ -2515,7 +2520,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="3"/>
     </row>
-    <row r="109" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>53.5</v>
       </c>
@@ -2532,7 +2537,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="3"/>
     </row>
-    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>54</v>
       </c>
@@ -2549,7 +2554,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="3"/>
     </row>
-    <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>54.5</v>
       </c>
@@ -2566,7 +2571,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="3"/>
     </row>
-    <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>55</v>
       </c>
@@ -2583,7 +2588,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="3"/>
     </row>
-    <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>55.5</v>
       </c>
@@ -2600,7 +2605,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="3"/>
     </row>
-    <row r="114" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>56</v>
       </c>
@@ -2617,7 +2622,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="3"/>
     </row>
-    <row r="115" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>56.5</v>
       </c>
@@ -2634,7 +2639,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="3"/>
     </row>
-    <row r="116" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>57</v>
       </c>
@@ -2651,7 +2656,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="3"/>
     </row>
-    <row r="117" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>57.5</v>
       </c>
@@ -2668,7 +2673,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="3"/>
     </row>
-    <row r="118" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>58</v>
       </c>
@@ -2685,7 +2690,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="3"/>
     </row>
-    <row r="119" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>58.5</v>
       </c>
@@ -2702,7 +2707,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="3"/>
     </row>
-    <row r="120" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>59</v>
       </c>
@@ -2719,7 +2724,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="3"/>
     </row>
-    <row r="121" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>59.5</v>
       </c>
@@ -2736,7 +2741,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="3"/>
     </row>
-    <row r="122" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>60</v>
       </c>
@@ -2774,7 +2779,7 @@
         <v>6.1872649800000001</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>60.5</v>
       </c>
@@ -2791,7 +2796,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="3"/>
     </row>
-    <row r="124" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>61</v>
       </c>
@@ -2808,7 +2813,7 @@
       <c r="F124" s="1"/>
       <c r="G124" s="3"/>
     </row>
-    <row r="125" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>61.5</v>
       </c>
@@ -2825,7 +2830,7 @@
       <c r="F125" s="1"/>
       <c r="G125" s="3"/>
     </row>
-    <row r="126" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>62</v>
       </c>
@@ -2842,7 +2847,7 @@
       <c r="F126" s="1"/>
       <c r="G126" s="3"/>
     </row>
-    <row r="127" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>62.5</v>
       </c>
@@ -2859,7 +2864,7 @@
       <c r="F127" s="1"/>
       <c r="G127" s="3"/>
     </row>
-    <row r="128" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>63</v>
       </c>
@@ -2876,7 +2881,7 @@
       <c r="F128" s="1"/>
       <c r="G128" s="3"/>
     </row>
-    <row r="129" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>63.5</v>
       </c>
@@ -2893,7 +2898,7 @@
       <c r="F129" s="1"/>
       <c r="G129" s="3"/>
     </row>
-    <row r="130" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>64</v>
       </c>
@@ -2910,7 +2915,7 @@
       <c r="F130" s="1"/>
       <c r="G130" s="3"/>
     </row>
-    <row r="131" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>64.5</v>
       </c>
@@ -2927,7 +2932,7 @@
       <c r="F131" s="1"/>
       <c r="G131" s="3"/>
     </row>
-    <row r="132" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>65</v>
       </c>
@@ -2944,7 +2949,7 @@
       <c r="F132" s="1"/>
       <c r="G132" s="3"/>
     </row>
-    <row r="133" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>65.5</v>
       </c>
@@ -2961,7 +2966,7 @@
       <c r="F133" s="1"/>
       <c r="G133" s="3"/>
     </row>
-    <row r="134" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>66</v>
       </c>
@@ -2978,7 +2983,7 @@
       <c r="F134" s="1"/>
       <c r="G134" s="3"/>
     </row>
-    <row r="135" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>66.5</v>
       </c>
@@ -2995,7 +3000,7 @@
       <c r="F135" s="1"/>
       <c r="G135" s="3"/>
     </row>
-    <row r="136" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>67</v>
       </c>
@@ -3012,7 +3017,7 @@
       <c r="F136" s="1"/>
       <c r="G136" s="3"/>
     </row>
-    <row r="137" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>67.5</v>
       </c>
@@ -3029,7 +3034,7 @@
       <c r="F137" s="1"/>
       <c r="G137" s="3"/>
     </row>
-    <row r="138" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>68</v>
       </c>
@@ -3046,7 +3051,7 @@
       <c r="F138" s="1"/>
       <c r="G138" s="3"/>
     </row>
-    <row r="139" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>68.5</v>
       </c>
@@ -3063,7 +3068,7 @@
       <c r="F139" s="1"/>
       <c r="G139" s="3"/>
     </row>
-    <row r="140" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>69</v>
       </c>
@@ -3080,7 +3085,7 @@
       <c r="F140" s="1"/>
       <c r="G140" s="3"/>
     </row>
-    <row r="141" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>69.5</v>
       </c>
@@ -3097,7 +3102,7 @@
       <c r="F141" s="1"/>
       <c r="G141" s="3"/>
     </row>
-    <row r="142" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>70</v>
       </c>
@@ -3114,7 +3119,7 @@
       <c r="F142" s="1"/>
       <c r="G142" s="3"/>
     </row>
-    <row r="143" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>70.5</v>
       </c>
@@ -3131,7 +3136,7 @@
       <c r="F143" s="1"/>
       <c r="G143" s="3"/>
     </row>
-    <row r="144" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>71</v>
       </c>
@@ -3148,7 +3153,7 @@
       <c r="F144" s="1"/>
       <c r="G144" s="3"/>
     </row>
-    <row r="145" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>71.5</v>
       </c>
@@ -3165,7 +3170,7 @@
       <c r="F145" s="1"/>
       <c r="G145" s="3"/>
     </row>
-    <row r="146" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>72</v>
       </c>
@@ -3182,7 +3187,7 @@
       <c r="F146" s="1"/>
       <c r="G146" s="3"/>
     </row>
-    <row r="147" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>72.5</v>
       </c>
@@ -3199,7 +3204,7 @@
       <c r="F147" s="1"/>
       <c r="G147" s="3"/>
     </row>
-    <row r="148" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>73</v>
       </c>
@@ -3216,7 +3221,7 @@
       <c r="F148" s="1"/>
       <c r="G148" s="3"/>
     </row>
-    <row r="149" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>73.5</v>
       </c>
@@ -3233,7 +3238,7 @@
       <c r="F149" s="1"/>
       <c r="G149" s="3"/>
     </row>
-    <row r="150" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>74</v>
       </c>
@@ -3250,7 +3255,7 @@
       <c r="F150" s="1"/>
       <c r="G150" s="3"/>
     </row>
-    <row r="151" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>74.5</v>
       </c>
@@ -3267,7 +3272,7 @@
       <c r="F151" s="1"/>
       <c r="G151" s="3"/>
     </row>
-    <row r="152" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>75</v>
       </c>
@@ -3284,7 +3289,7 @@
       <c r="F152" s="1"/>
       <c r="G152" s="3"/>
     </row>
-    <row r="153" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>75.5</v>
       </c>
@@ -3301,7 +3306,7 @@
       <c r="F153" s="1"/>
       <c r="G153" s="3"/>
     </row>
-    <row r="154" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>76</v>
       </c>
@@ -3318,7 +3323,7 @@
       <c r="F154" s="1"/>
       <c r="G154" s="3"/>
     </row>
-    <row r="155" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>76.5</v>
       </c>
@@ -3335,7 +3340,7 @@
       <c r="F155" s="1"/>
       <c r="G155" s="3"/>
     </row>
-    <row r="156" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>77</v>
       </c>
@@ -3352,7 +3357,7 @@
       <c r="F156" s="1"/>
       <c r="G156" s="3"/>
     </row>
-    <row r="157" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>77.5</v>
       </c>
@@ -3369,7 +3374,7 @@
       <c r="F157" s="1"/>
       <c r="G157" s="3"/>
     </row>
-    <row r="158" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>78</v>
       </c>
@@ -3386,7 +3391,7 @@
       <c r="F158" s="1"/>
       <c r="G158" s="3"/>
     </row>
-    <row r="159" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>78.5</v>
       </c>
@@ -3403,7 +3408,7 @@
       <c r="F159" s="1"/>
       <c r="G159" s="3"/>
     </row>
-    <row r="160" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>79</v>
       </c>
@@ -3420,7 +3425,7 @@
       <c r="F160" s="1"/>
       <c r="G160" s="3"/>
     </row>
-    <row r="161" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>79.5</v>
       </c>
@@ -3437,7 +3442,7 @@
       <c r="F161" s="1"/>
       <c r="G161" s="3"/>
     </row>
-    <row r="162" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>80</v>
       </c>
@@ -3454,7 +3459,7 @@
       <c r="F162" s="1"/>
       <c r="G162" s="3"/>
     </row>
-    <row r="163" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>80.5</v>
       </c>
@@ -3471,7 +3476,7 @@
       <c r="F163" s="1"/>
       <c r="G163" s="3"/>
     </row>
-    <row r="164" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>81</v>
       </c>
@@ -3488,7 +3493,7 @@
       <c r="F164" s="1"/>
       <c r="G164" s="3"/>
     </row>
-    <row r="165" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>81.5</v>
       </c>
@@ -3505,7 +3510,7 @@
       <c r="F165" s="1"/>
       <c r="G165" s="3"/>
     </row>
-    <row r="166" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>82</v>
       </c>
@@ -3522,7 +3527,7 @@
       <c r="F166" s="1"/>
       <c r="G166" s="3"/>
     </row>
-    <row r="167" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>82.5</v>
       </c>
@@ -3539,7 +3544,7 @@
       <c r="F167" s="1"/>
       <c r="G167" s="3"/>
     </row>
-    <row r="168" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>83</v>
       </c>
@@ -3556,7 +3561,7 @@
       <c r="F168" s="1"/>
       <c r="G168" s="3"/>
     </row>
-    <row r="169" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>83.5</v>
       </c>
@@ -3573,7 +3578,7 @@
       <c r="F169" s="1"/>
       <c r="G169" s="3"/>
     </row>
-    <row r="170" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>84</v>
       </c>
@@ -3590,7 +3595,7 @@
       <c r="F170" s="1"/>
       <c r="G170" s="3"/>
     </row>
-    <row r="171" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>84.5</v>
       </c>
@@ -3607,7 +3612,7 @@
       <c r="F171" s="1"/>
       <c r="G171" s="3"/>
     </row>
-    <row r="172" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>85</v>
       </c>
@@ -3624,7 +3629,7 @@
       <c r="F172" s="1"/>
       <c r="G172" s="3"/>
     </row>
-    <row r="173" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>85.5</v>
       </c>
@@ -3641,7 +3646,7 @@
       <c r="F173" s="1"/>
       <c r="G173" s="3"/>
     </row>
-    <row r="174" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>86</v>
       </c>
@@ -3658,7 +3663,7 @@
       <c r="F174" s="1"/>
       <c r="G174" s="3"/>
     </row>
-    <row r="175" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>86.5</v>
       </c>
@@ -3675,7 +3680,7 @@
       <c r="F175" s="1"/>
       <c r="G175" s="3"/>
     </row>
-    <row r="176" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>87</v>
       </c>
@@ -3692,7 +3697,7 @@
       <c r="F176" s="1"/>
       <c r="G176" s="3"/>
     </row>
-    <row r="177" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>87.5</v>
       </c>
@@ -3709,7 +3714,7 @@
       <c r="F177" s="1"/>
       <c r="G177" s="3"/>
     </row>
-    <row r="178" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>88</v>
       </c>
@@ -3726,7 +3731,7 @@
       <c r="F178" s="1"/>
       <c r="G178" s="3"/>
     </row>
-    <row r="179" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>88.5</v>
       </c>
@@ -3743,7 +3748,7 @@
       <c r="F179" s="1"/>
       <c r="G179" s="3"/>
     </row>
-    <row r="180" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>89</v>
       </c>
@@ -3760,7 +3765,7 @@
       <c r="F180" s="1"/>
       <c r="G180" s="3"/>
     </row>
-    <row r="181" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>89.5</v>
       </c>
@@ -3777,7 +3782,7 @@
       <c r="F181" s="1"/>
       <c r="G181" s="3"/>
     </row>
-    <row r="182" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>90</v>
       </c>
@@ -3794,7 +3799,7 @@
       <c r="F182" s="1"/>
       <c r="G182" s="3"/>
     </row>
-    <row r="183" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>90.5</v>
       </c>
@@ -3811,7 +3816,7 @@
       <c r="F183" s="1"/>
       <c r="G183" s="3"/>
     </row>
-    <row r="184" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>91</v>
       </c>
@@ -3828,7 +3833,7 @@
       <c r="F184" s="1"/>
       <c r="G184" s="3"/>
     </row>
-    <row r="185" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>91.5</v>
       </c>
@@ -3845,7 +3850,7 @@
       <c r="F185" s="1"/>
       <c r="G185" s="3"/>
     </row>
-    <row r="186" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>92</v>
       </c>
@@ -3862,7 +3867,7 @@
       <c r="F186" s="1"/>
       <c r="G186" s="3"/>
     </row>
-    <row r="187" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>92.5</v>
       </c>
@@ -3879,7 +3884,7 @@
       <c r="F187" s="1"/>
       <c r="G187" s="3"/>
     </row>
-    <row r="188" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>93</v>
       </c>
@@ -3896,7 +3901,7 @@
       <c r="F188" s="1"/>
       <c r="G188" s="3"/>
     </row>
-    <row r="189" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>93.5</v>
       </c>
@@ -3913,7 +3918,7 @@
       <c r="F189" s="1"/>
       <c r="G189" s="3"/>
     </row>
-    <row r="190" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>94</v>
       </c>
@@ -3930,7 +3935,7 @@
       <c r="F190" s="1"/>
       <c r="G190" s="3"/>
     </row>
-    <row r="191" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>94.5</v>
       </c>
@@ -3947,7 +3952,7 @@
       <c r="F191" s="1"/>
       <c r="G191" s="3"/>
     </row>
-    <row r="192" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>95</v>
       </c>
@@ -3964,7 +3969,7 @@
       <c r="F192" s="1"/>
       <c r="G192" s="3"/>
     </row>
-    <row r="193" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>95.5</v>
       </c>
@@ -3981,7 +3986,7 @@
       <c r="F193" s="1"/>
       <c r="G193" s="3"/>
     </row>
-    <row r="194" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>96</v>
       </c>
@@ -3998,7 +4003,7 @@
       <c r="F194" s="1"/>
       <c r="G194" s="3"/>
     </row>
-    <row r="195" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>96.5</v>
       </c>
@@ -4015,7 +4020,7 @@
       <c r="F195" s="1"/>
       <c r="G195" s="3"/>
     </row>
-    <row r="196" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>97</v>
       </c>
@@ -4032,7 +4037,7 @@
       <c r="F196" s="1"/>
       <c r="G196" s="3"/>
     </row>
-    <row r="197" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>97.5</v>
       </c>
@@ -4049,7 +4054,7 @@
       <c r="F197" s="1"/>
       <c r="G197" s="3"/>
     </row>
-    <row r="198" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>98</v>
       </c>
@@ -4066,7 +4071,7 @@
       <c r="F198" s="1"/>
       <c r="G198" s="3"/>
     </row>
-    <row r="199" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>98.5</v>
       </c>
@@ -4083,7 +4088,7 @@
       <c r="F199" s="1"/>
       <c r="G199" s="3"/>
     </row>
-    <row r="200" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>99</v>
       </c>
@@ -4100,7 +4105,7 @@
       <c r="F200" s="1"/>
       <c r="G200" s="3"/>
     </row>
-    <row r="201" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>99.5</v>
       </c>
@@ -4117,7 +4122,7 @@
       <c r="F201" s="1"/>
       <c r="G201" s="3"/>
     </row>
-    <row r="202" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>100</v>
       </c>
@@ -4155,7 +4160,7 @@
         <v>4.8796937529999997</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>100.5</v>
       </c>
@@ -4172,7 +4177,7 @@
       <c r="F203" s="1"/>
       <c r="G203" s="3"/>
     </row>
-    <row r="204" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>101</v>
       </c>
@@ -4189,7 +4194,7 @@
       <c r="F204" s="1"/>
       <c r="G204" s="3"/>
     </row>
-    <row r="205" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>101.5</v>
       </c>
@@ -4206,7 +4211,7 @@
       <c r="F205" s="1"/>
       <c r="G205" s="3"/>
     </row>
-    <row r="206" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>102</v>
       </c>
@@ -4223,7 +4228,7 @@
       <c r="F206" s="1"/>
       <c r="G206" s="3"/>
     </row>
-    <row r="207" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>102.5</v>
       </c>
@@ -4240,7 +4245,7 @@
       <c r="F207" s="1"/>
       <c r="G207" s="3"/>
     </row>
-    <row r="208" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>103</v>
       </c>
@@ -4257,7 +4262,7 @@
       <c r="F208" s="1"/>
       <c r="G208" s="3"/>
     </row>
-    <row r="209" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>103.5</v>
       </c>
@@ -4274,7 +4279,7 @@
       <c r="F209" s="1"/>
       <c r="G209" s="3"/>
     </row>
-    <row r="210" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>104</v>
       </c>
@@ -4291,7 +4296,7 @@
       <c r="F210" s="1"/>
       <c r="G210" s="3"/>
     </row>
-    <row r="211" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>104.5</v>
       </c>
@@ -4308,7 +4313,7 @@
       <c r="F211" s="1"/>
       <c r="G211" s="3"/>
     </row>
-    <row r="212" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>105</v>
       </c>
@@ -4325,7 +4330,7 @@
       <c r="F212" s="1"/>
       <c r="G212" s="3"/>
     </row>
-    <row r="213" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>105.5</v>
       </c>
@@ -4342,7 +4347,7 @@
       <c r="F213" s="1"/>
       <c r="G213" s="3"/>
     </row>
-    <row r="214" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>106</v>
       </c>
@@ -4359,7 +4364,7 @@
       <c r="F214" s="1"/>
       <c r="G214" s="3"/>
     </row>
-    <row r="215" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>106.5</v>
       </c>
@@ -4376,7 +4381,7 @@
       <c r="F215" s="1"/>
       <c r="G215" s="3"/>
     </row>
-    <row r="216" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>107</v>
       </c>
@@ -4393,7 +4398,7 @@
       <c r="F216" s="1"/>
       <c r="G216" s="3"/>
     </row>
-    <row r="217" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>107.5</v>
       </c>
@@ -4410,7 +4415,7 @@
       <c r="F217" s="1"/>
       <c r="G217" s="3"/>
     </row>
-    <row r="218" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>108</v>
       </c>
@@ -4427,7 +4432,7 @@
       <c r="F218" s="1"/>
       <c r="G218" s="3"/>
     </row>
-    <row r="219" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>108.5</v>
       </c>
@@ -4444,7 +4449,7 @@
       <c r="F219" s="1"/>
       <c r="G219" s="3"/>
     </row>
-    <row r="220" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>109</v>
       </c>
@@ -4461,7 +4466,7 @@
       <c r="F220" s="1"/>
       <c r="G220" s="3"/>
     </row>
-    <row r="221" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>109.5</v>
       </c>
@@ -4478,7 +4483,7 @@
       <c r="F221" s="1"/>
       <c r="G221" s="3"/>
     </row>
-    <row r="222" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>110</v>
       </c>
@@ -4495,7 +4500,7 @@
       <c r="F222" s="1"/>
       <c r="G222" s="3"/>
     </row>
-    <row r="223" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>110.5</v>
       </c>
@@ -4512,7 +4517,7 @@
       <c r="F223" s="1"/>
       <c r="G223" s="3"/>
     </row>
-    <row r="224" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>111</v>
       </c>
@@ -4529,7 +4534,7 @@
       <c r="F224" s="1"/>
       <c r="G224" s="3"/>
     </row>
-    <row r="225" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>111.5</v>
       </c>
@@ -4546,7 +4551,7 @@
       <c r="F225" s="1"/>
       <c r="G225" s="3"/>
     </row>
-    <row r="226" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>112</v>
       </c>
@@ -4563,7 +4568,7 @@
       <c r="F226" s="1"/>
       <c r="G226" s="3"/>
     </row>
-    <row r="227" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>112.5</v>
       </c>
@@ -4580,7 +4585,7 @@
       <c r="F227" s="1"/>
       <c r="G227" s="3"/>
     </row>
-    <row r="228" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>113</v>
       </c>
@@ -4597,7 +4602,7 @@
       <c r="F228" s="1"/>
       <c r="G228" s="3"/>
     </row>
-    <row r="229" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>113.5</v>
       </c>
@@ -4614,7 +4619,7 @@
       <c r="F229" s="1"/>
       <c r="G229" s="3"/>
     </row>
-    <row r="230" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>114</v>
       </c>
@@ -4631,7 +4636,7 @@
       <c r="F230" s="1"/>
       <c r="G230" s="3"/>
     </row>
-    <row r="231" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>114.5</v>
       </c>
@@ -4648,7 +4653,7 @@
       <c r="F231" s="1"/>
       <c r="G231" s="3"/>
     </row>
-    <row r="232" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>115</v>
       </c>
@@ -4665,7 +4670,7 @@
       <c r="F232" s="1"/>
       <c r="G232" s="3"/>
     </row>
-    <row r="233" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>115.5</v>
       </c>
@@ -4682,7 +4687,7 @@
       <c r="F233" s="1"/>
       <c r="G233" s="3"/>
     </row>
-    <row r="234" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>116</v>
       </c>
@@ -4699,7 +4704,7 @@
       <c r="F234" s="1"/>
       <c r="G234" s="3"/>
     </row>
-    <row r="235" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>116.5</v>
       </c>
@@ -4716,7 +4721,7 @@
       <c r="F235" s="1"/>
       <c r="G235" s="3"/>
     </row>
-    <row r="236" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>117</v>
       </c>
@@ -4733,7 +4738,7 @@
       <c r="F236" s="1"/>
       <c r="G236" s="3"/>
     </row>
-    <row r="237" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>117.5</v>
       </c>
@@ -4750,7 +4755,7 @@
       <c r="F237" s="1"/>
       <c r="G237" s="3"/>
     </row>
-    <row r="238" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>118</v>
       </c>
@@ -4767,7 +4772,7 @@
       <c r="F238" s="1"/>
       <c r="G238" s="3"/>
     </row>
-    <row r="239" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>118.5</v>
       </c>
@@ -4784,7 +4789,7 @@
       <c r="F239" s="1"/>
       <c r="G239" s="3"/>
     </row>
-    <row r="240" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>119</v>
       </c>
@@ -4801,7 +4806,7 @@
       <c r="F240" s="1"/>
       <c r="G240" s="3"/>
     </row>
-    <row r="241" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>119.5</v>
       </c>
@@ -4818,7 +4823,7 @@
       <c r="F241" s="1"/>
       <c r="G241" s="3"/>
     </row>
-    <row r="242" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>120</v>
       </c>
@@ -4856,277 +4861,277 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B243" s="2"/>
       <c r="C243" s="1"/>
       <c r="D243" s="2"/>
     </row>
-    <row r="244" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B244" s="2"/>
       <c r="C244" s="1"/>
       <c r="D244" s="2"/>
     </row>
-    <row r="245" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B245" s="2"/>
       <c r="C245" s="1"/>
       <c r="D245" s="2"/>
     </row>
-    <row r="246" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B246" s="2"/>
       <c r="C246" s="1"/>
       <c r="D246" s="2"/>
     </row>
-    <row r="247" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B247" s="2"/>
       <c r="C247" s="1"/>
       <c r="D247" s="2"/>
     </row>
-    <row r="248" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B248" s="2"/>
       <c r="C248" s="1"/>
       <c r="D248" s="2"/>
     </row>
-    <row r="249" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B249" s="2"/>
       <c r="C249" s="1"/>
       <c r="D249" s="2"/>
     </row>
-    <row r="250" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B250" s="2"/>
       <c r="C250" s="1"/>
       <c r="D250" s="2"/>
     </row>
-    <row r="251" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B251" s="2"/>
       <c r="C251" s="1"/>
       <c r="D251" s="2"/>
     </row>
-    <row r="252" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B252" s="2"/>
       <c r="C252" s="1"/>
       <c r="D252" s="2"/>
     </row>
-    <row r="253" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B253" s="2"/>
       <c r="C253" s="1"/>
       <c r="D253" s="2"/>
     </row>
-    <row r="254" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B254" s="2"/>
       <c r="C254" s="1"/>
       <c r="D254" s="2"/>
     </row>
-    <row r="255" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B255" s="2"/>
       <c r="C255" s="1"/>
       <c r="D255" s="2"/>
     </row>
-    <row r="256" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B256" s="2"/>
       <c r="C256" s="1"/>
       <c r="D256" s="2"/>
     </row>
-    <row r="257" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B257" s="2"/>
       <c r="C257" s="1"/>
       <c r="D257" s="2"/>
     </row>
-    <row r="258" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B258" s="2"/>
       <c r="C258" s="1"/>
       <c r="D258" s="2"/>
     </row>
-    <row r="259" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B259" s="2"/>
       <c r="C259" s="1"/>
       <c r="D259" s="2"/>
     </row>
-    <row r="260" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B260" s="2"/>
       <c r="C260" s="1"/>
       <c r="D260" s="2"/>
     </row>
-    <row r="261" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B261" s="2"/>
       <c r="D261" s="2"/>
     </row>
-    <row r="262" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B262" s="2"/>
       <c r="D262" s="2"/>
     </row>
-    <row r="263" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B263" s="2"/>
       <c r="D263" s="2"/>
     </row>
-    <row r="264" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B264" s="2"/>
       <c r="D264" s="2"/>
     </row>
-    <row r="265" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B265" s="2"/>
       <c r="D265" s="2"/>
     </row>
-    <row r="266" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B266" s="2"/>
       <c r="D266" s="2"/>
     </row>
-    <row r="267" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B267" s="2"/>
       <c r="D267" s="2"/>
     </row>
-    <row r="268" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B268" s="2"/>
       <c r="D268" s="2"/>
     </row>
-    <row r="269" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B269" s="2"/>
       <c r="D269" s="2"/>
     </row>
-    <row r="270" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B270" s="2"/>
       <c r="D270" s="2"/>
     </row>
-    <row r="271" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B271" s="2"/>
       <c r="D271" s="2"/>
     </row>
-    <row r="272" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B272" s="2"/>
       <c r="D272" s="2"/>
     </row>
-    <row r="273" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B273" s="2"/>
       <c r="D273" s="2"/>
     </row>
-    <row r="274" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B274" s="2"/>
       <c r="D274" s="2"/>
     </row>
-    <row r="275" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B275" s="2"/>
       <c r="D275" s="2"/>
     </row>
-    <row r="276" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B276" s="2"/>
       <c r="D276" s="2"/>
     </row>
-    <row r="277" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B277" s="2"/>
       <c r="D277" s="2"/>
     </row>
-    <row r="278" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B278" s="2"/>
       <c r="D278" s="2"/>
     </row>
-    <row r="279" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B279" s="2"/>
       <c r="D279" s="2"/>
     </row>
-    <row r="280" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B280" s="2"/>
       <c r="D280" s="2"/>
     </row>
-    <row r="281" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B281" s="2"/>
       <c r="D281" s="2"/>
     </row>
-    <row r="282" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B282" s="2"/>
       <c r="D282" s="2"/>
     </row>
-    <row r="283" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B283" s="2"/>
       <c r="D283" s="2"/>
     </row>
-    <row r="284" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B284" s="2"/>
       <c r="D284" s="2"/>
     </row>
-    <row r="285" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B285" s="2"/>
       <c r="D285" s="2"/>
     </row>
-    <row r="286" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B286" s="2"/>
       <c r="D286" s="2"/>
     </row>
-    <row r="287" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B287" s="2"/>
       <c r="D287" s="2"/>
     </row>
-    <row r="288" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B288" s="2"/>
       <c r="D288" s="2"/>
     </row>
-    <row r="289" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B289" s="2"/>
       <c r="D289" s="2"/>
     </row>
-    <row r="290" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B290" s="2"/>
       <c r="D290" s="2"/>
     </row>
-    <row r="291" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B291" s="2"/>
       <c r="D291" s="2"/>
     </row>
-    <row r="292" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B292" s="2"/>
       <c r="D292" s="2"/>
     </row>
-    <row r="293" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B293" s="2"/>
       <c r="D293" s="2"/>
     </row>
-    <row r="294" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B294" s="2"/>
       <c r="D294" s="2"/>
     </row>
-    <row r="295" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B295" s="2"/>
       <c r="D295" s="2"/>
     </row>
-    <row r="296" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B296" s="2"/>
       <c r="D296" s="2"/>
     </row>
-    <row r="297" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B297" s="2"/>
       <c r="D297" s="2"/>
     </row>
-    <row r="298" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B298" s="2"/>
       <c r="D298" s="2"/>
     </row>
-    <row r="299" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B299" s="2"/>
       <c r="D299" s="2"/>
     </row>
-    <row r="300" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B300" s="2"/>
       <c r="D300" s="2"/>
     </row>
-    <row r="301" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B301" s="2"/>
       <c r="D301" s="2"/>
     </row>
-    <row r="302" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B302" s="2"/>
       <c r="D302" s="2"/>
     </row>
-    <row r="303" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B303" s="2"/>
       <c r="D303" s="2"/>
     </row>
-    <row r="304" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B304" s="2"/>
       <c r="D304" s="2"/>
     </row>
-    <row r="305" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B305" s="2"/>
       <c r="D305" s="2"/>
     </row>
-    <row r="306" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B306" s="2"/>
       <c r="D306" s="2"/>
     </row>
@@ -5138,9 +5143,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B23A2748-2DBF-42E7-B7EC-F7EED76B1876}">
   <dimension ref="A1:N306"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -5184,7 +5189,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -5228,7 +5233,7 @@
         <v>11.568</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0.5</v>
       </c>
@@ -5249,7 +5254,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -5270,7 +5275,7 @@
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1.5</v>
       </c>
@@ -5291,7 +5296,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -5312,7 +5317,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2.5</v>
       </c>
@@ -5333,7 +5338,7 @@
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -5354,7 +5359,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3.5</v>
       </c>
@@ -5375,7 +5380,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>4</v>
       </c>
@@ -5419,7 +5424,7 @@
         <v>10.802</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>4.5</v>
       </c>
@@ -5440,7 +5445,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5</v>
       </c>
@@ -5461,7 +5466,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>5.5</v>
       </c>
@@ -5482,7 +5487,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>6</v>
       </c>
@@ -5503,7 +5508,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>6.5</v>
       </c>
@@ -5524,7 +5529,7 @@
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>7</v>
       </c>
@@ -5545,7 +5550,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>7.5</v>
       </c>
@@ -5566,7 +5571,7 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -5610,7 +5615,7 @@
         <v>10.162000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>8.5</v>
       </c>
@@ -5631,7 +5636,7 @@
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>9</v>
       </c>
@@ -5652,7 +5657,7 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>9.5</v>
       </c>
@@ -5673,7 +5678,7 @@
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>10</v>
       </c>
@@ -5694,7 +5699,7 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>10.5</v>
       </c>
@@ -5715,7 +5720,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>11</v>
       </c>
@@ -5736,7 +5741,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>11.5</v>
       </c>
@@ -5757,7 +5762,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>12</v>
       </c>
@@ -5778,7 +5783,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>12.5</v>
       </c>
@@ -5799,7 +5804,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>13</v>
       </c>
@@ -5843,7 +5848,7 @@
         <v>11.718</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>13.5</v>
       </c>
@@ -5864,7 +5869,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>14</v>
       </c>
@@ -5885,7 +5890,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>14.5</v>
       </c>
@@ -5906,7 +5911,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>15</v>
       </c>
@@ -5927,7 +5932,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>15.5</v>
       </c>
@@ -5948,7 +5953,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>16</v>
       </c>
@@ -5969,7 +5974,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>16.5</v>
       </c>
@@ -5990,7 +5995,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>17</v>
       </c>
@@ -6011,7 +6016,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>17.5</v>
       </c>
@@ -6032,7 +6037,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>18</v>
       </c>
@@ -6076,7 +6081,7 @@
         <v>9.4920000000000009</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>18.5</v>
       </c>
@@ -6097,7 +6102,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>19</v>
       </c>
@@ -6118,7 +6123,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>19.5</v>
       </c>
@@ -6139,7 +6144,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>20</v>
       </c>
@@ -6160,7 +6165,7 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>20.5</v>
       </c>
@@ -6181,7 +6186,7 @@
       </c>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>21</v>
       </c>
@@ -6202,7 +6207,7 @@
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>21.5</v>
       </c>
@@ -6223,7 +6228,7 @@
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>22</v>
       </c>
@@ -6244,7 +6249,7 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>22.5</v>
       </c>
@@ -6265,7 +6270,7 @@
       </c>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>23</v>
       </c>
@@ -6309,7 +6314,7 @@
         <v>9.8439999999999994</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>23.5</v>
       </c>
@@ -6330,7 +6335,7 @@
       </c>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>24</v>
       </c>
@@ -6351,7 +6356,7 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>24.5</v>
       </c>
@@ -6372,7 +6377,7 @@
       </c>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>25</v>
       </c>
@@ -6393,7 +6398,7 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>25.5</v>
       </c>
@@ -6414,7 +6419,7 @@
       </c>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>26</v>
       </c>
@@ -6435,7 +6440,7 @@
       </c>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>26.5</v>
       </c>
@@ -6456,7 +6461,7 @@
       </c>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>27</v>
       </c>
@@ -6477,7 +6482,7 @@
       </c>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>27.5</v>
       </c>
@@ -6498,7 +6503,7 @@
       </c>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>28</v>
       </c>
@@ -6519,7 +6524,7 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>28.5</v>
       </c>
@@ -6540,7 +6545,7 @@
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>29</v>
       </c>
@@ -6561,7 +6566,7 @@
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>29.5</v>
       </c>
@@ -6582,7 +6587,7 @@
       </c>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>30</v>
       </c>
@@ -6603,7 +6608,7 @@
       </c>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>30.5</v>
       </c>
@@ -6624,7 +6629,7 @@
       </c>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>31</v>
       </c>
@@ -6668,7 +6673,7 @@
         <v>7.5780000000000003</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>31.5</v>
       </c>
@@ -6689,7 +6694,7 @@
       </c>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>32</v>
       </c>
@@ -6710,7 +6715,7 @@
       </c>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>32.5</v>
       </c>
@@ -6731,7 +6736,7 @@
       </c>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>33</v>
       </c>
@@ -6752,7 +6757,7 @@
       </c>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>33.5</v>
       </c>
@@ -6773,7 +6778,7 @@
       </c>
       <c r="J69" s="3"/>
     </row>
-    <row r="70" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>34</v>
       </c>
@@ -6794,7 +6799,7 @@
       </c>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>34.5</v>
       </c>
@@ -6815,7 +6820,7 @@
       </c>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>35</v>
       </c>
@@ -6836,7 +6841,7 @@
       </c>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>35.5</v>
       </c>
@@ -6857,7 +6862,7 @@
       </c>
       <c r="J73" s="3"/>
     </row>
-    <row r="74" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>36</v>
       </c>
@@ -6878,7 +6883,7 @@
       </c>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>36.5</v>
       </c>
@@ -6899,7 +6904,7 @@
       </c>
       <c r="J75" s="3"/>
     </row>
-    <row r="76" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>37</v>
       </c>
@@ -6920,7 +6925,7 @@
       </c>
       <c r="J76" s="3"/>
     </row>
-    <row r="77" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>37.5</v>
       </c>
@@ -6941,7 +6946,7 @@
       </c>
       <c r="J77" s="3"/>
     </row>
-    <row r="78" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>38</v>
       </c>
@@ -6962,7 +6967,7 @@
       </c>
       <c r="J78" s="3"/>
     </row>
-    <row r="79" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>38.5</v>
       </c>
@@ -6983,7 +6988,7 @@
       </c>
       <c r="J79" s="3"/>
     </row>
-    <row r="80" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>39</v>
       </c>
@@ -7004,7 +7009,7 @@
       </c>
       <c r="J80" s="3"/>
     </row>
-    <row r="81" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>39.5</v>
       </c>
@@ -7025,7 +7030,7 @@
       </c>
       <c r="J81" s="3"/>
     </row>
-    <row r="82" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>40</v>
       </c>
@@ -7046,7 +7051,7 @@
       </c>
       <c r="J82" s="3"/>
     </row>
-    <row r="83" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>40.5</v>
       </c>
@@ -7067,7 +7072,7 @@
       </c>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>41</v>
       </c>
@@ -7088,7 +7093,7 @@
       </c>
       <c r="J84" s="3"/>
     </row>
-    <row r="85" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>41.5</v>
       </c>
@@ -7109,7 +7114,7 @@
       </c>
       <c r="J85" s="3"/>
     </row>
-    <row r="86" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>42</v>
       </c>
@@ -7130,7 +7135,7 @@
       </c>
       <c r="J86" s="3"/>
     </row>
-    <row r="87" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>42.5</v>
       </c>
@@ -7151,7 +7156,7 @@
       </c>
       <c r="J87" s="3"/>
     </row>
-    <row r="88" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>43</v>
       </c>
@@ -7195,7 +7200,7 @@
         <v>6.9420000000000002</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>43.5</v>
       </c>
@@ -7216,7 +7221,7 @@
       </c>
       <c r="J89" s="3"/>
     </row>
-    <row r="90" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>44</v>
       </c>
@@ -7237,7 +7242,7 @@
       </c>
       <c r="J90" s="3"/>
     </row>
-    <row r="91" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>44.5</v>
       </c>
@@ -7258,7 +7263,7 @@
       </c>
       <c r="J91" s="3"/>
     </row>
-    <row r="92" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45</v>
       </c>
@@ -7279,7 +7284,7 @@
       </c>
       <c r="J92" s="3"/>
     </row>
-    <row r="93" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45.5</v>
       </c>
@@ -7300,7 +7305,7 @@
       </c>
       <c r="J93" s="3"/>
     </row>
-    <row r="94" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46</v>
       </c>
@@ -7321,7 +7326,7 @@
       </c>
       <c r="J94" s="3"/>
     </row>
-    <row r="95" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46.5</v>
       </c>
@@ -7342,7 +7347,7 @@
       </c>
       <c r="J95" s="3"/>
     </row>
-    <row r="96" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>47</v>
       </c>
@@ -7363,7 +7368,7 @@
       </c>
       <c r="J96" s="3"/>
     </row>
-    <row r="97" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>47.5</v>
       </c>
@@ -7384,7 +7389,7 @@
       </c>
       <c r="J97" s="3"/>
     </row>
-    <row r="98" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>48</v>
       </c>
@@ -7405,7 +7410,7 @@
       </c>
       <c r="J98" s="3"/>
     </row>
-    <row r="99" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>48.5</v>
       </c>
@@ -7426,7 +7431,7 @@
       </c>
       <c r="J99" s="3"/>
     </row>
-    <row r="100" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>49</v>
       </c>
@@ -7447,7 +7452,7 @@
       </c>
       <c r="J100" s="3"/>
     </row>
-    <row r="101" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>49.5</v>
       </c>
@@ -7468,7 +7473,7 @@
       </c>
       <c r="J101" s="3"/>
     </row>
-    <row r="102" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>50</v>
       </c>
@@ -7489,7 +7494,7 @@
       </c>
       <c r="J102" s="3"/>
     </row>
-    <row r="103" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>50.5</v>
       </c>
@@ -7510,7 +7515,7 @@
       </c>
       <c r="J103" s="3"/>
     </row>
-    <row r="104" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>51</v>
       </c>
@@ -7531,7 +7536,7 @@
       </c>
       <c r="J104" s="3"/>
     </row>
-    <row r="105" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>51.5</v>
       </c>
@@ -7552,7 +7557,7 @@
       </c>
       <c r="J105" s="3"/>
     </row>
-    <row r="106" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>52</v>
       </c>
@@ -7573,7 +7578,7 @@
       </c>
       <c r="J106" s="3"/>
     </row>
-    <row r="107" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>52.5</v>
       </c>
@@ -7594,7 +7599,7 @@
       </c>
       <c r="J107" s="3"/>
     </row>
-    <row r="108" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>53</v>
       </c>
@@ -7615,7 +7620,7 @@
       </c>
       <c r="J108" s="3"/>
     </row>
-    <row r="109" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>53.5</v>
       </c>
@@ -7636,7 +7641,7 @@
       </c>
       <c r="J109" s="3"/>
     </row>
-    <row r="110" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>54</v>
       </c>
@@ -7657,7 +7662,7 @@
       </c>
       <c r="J110" s="3"/>
     </row>
-    <row r="111" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>54.5</v>
       </c>
@@ -7678,7 +7683,7 @@
       </c>
       <c r="J111" s="3"/>
     </row>
-    <row r="112" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>55</v>
       </c>
@@ -7699,7 +7704,7 @@
       </c>
       <c r="J112" s="3"/>
     </row>
-    <row r="113" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>55.5</v>
       </c>
@@ -7720,7 +7725,7 @@
       </c>
       <c r="J113" s="3"/>
     </row>
-    <row r="114" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>56</v>
       </c>
@@ -7741,7 +7746,7 @@
       </c>
       <c r="J114" s="3"/>
     </row>
-    <row r="115" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>56.5</v>
       </c>
@@ -7762,7 +7767,7 @@
       </c>
       <c r="J115" s="3"/>
     </row>
-    <row r="116" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>57</v>
       </c>
@@ -7783,7 +7788,7 @@
       </c>
       <c r="J116" s="3"/>
     </row>
-    <row r="117" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>57.5</v>
       </c>
@@ -7804,7 +7809,7 @@
       </c>
       <c r="J117" s="3"/>
     </row>
-    <row r="118" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>58</v>
       </c>
@@ -7825,7 +7830,7 @@
       </c>
       <c r="J118" s="3"/>
     </row>
-    <row r="119" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>58.5</v>
       </c>
@@ -7846,7 +7851,7 @@
       </c>
       <c r="J119" s="3"/>
     </row>
-    <row r="120" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>59</v>
       </c>
@@ -7867,7 +7872,7 @@
       </c>
       <c r="J120" s="3"/>
     </row>
-    <row r="121" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>59.5</v>
       </c>
@@ -7888,7 +7893,7 @@
       </c>
       <c r="J121" s="3"/>
     </row>
-    <row r="122" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>60</v>
       </c>
@@ -7932,7 +7937,7 @@
         <v>4.9160000000000004</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>60.5</v>
       </c>
@@ -7953,7 +7958,7 @@
       </c>
       <c r="J123" s="3"/>
     </row>
-    <row r="124" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>61</v>
       </c>
@@ -7974,7 +7979,7 @@
       </c>
       <c r="J124" s="3"/>
     </row>
-    <row r="125" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>61.5</v>
       </c>
@@ -7995,7 +8000,7 @@
       </c>
       <c r="J125" s="3"/>
     </row>
-    <row r="126" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>62</v>
       </c>
@@ -8016,7 +8021,7 @@
       </c>
       <c r="J126" s="3"/>
     </row>
-    <row r="127" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>62.5</v>
       </c>
@@ -8037,7 +8042,7 @@
       </c>
       <c r="J127" s="3"/>
     </row>
-    <row r="128" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>63</v>
       </c>
@@ -8058,7 +8063,7 @@
       </c>
       <c r="J128" s="3"/>
     </row>
-    <row r="129" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>63.5</v>
       </c>
@@ -8079,7 +8084,7 @@
       </c>
       <c r="J129" s="3"/>
     </row>
-    <row r="130" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>64</v>
       </c>
@@ -8100,7 +8105,7 @@
       </c>
       <c r="J130" s="3"/>
     </row>
-    <row r="131" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>64.5</v>
       </c>
@@ -8121,7 +8126,7 @@
       </c>
       <c r="J131" s="3"/>
     </row>
-    <row r="132" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>65</v>
       </c>
@@ -8142,7 +8147,7 @@
       </c>
       <c r="J132" s="3"/>
     </row>
-    <row r="133" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>65.5</v>
       </c>
@@ -8163,7 +8168,7 @@
       </c>
       <c r="J133" s="3"/>
     </row>
-    <row r="134" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>66</v>
       </c>
@@ -8184,7 +8189,7 @@
       </c>
       <c r="J134" s="3"/>
     </row>
-    <row r="135" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>66.5</v>
       </c>
@@ -8205,7 +8210,7 @@
       </c>
       <c r="J135" s="3"/>
     </row>
-    <row r="136" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>67</v>
       </c>
@@ -8226,7 +8231,7 @@
       </c>
       <c r="J136" s="3"/>
     </row>
-    <row r="137" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>67.5</v>
       </c>
@@ -8247,7 +8252,7 @@
       </c>
       <c r="J137" s="3"/>
     </row>
-    <row r="138" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>68</v>
       </c>
@@ -8268,7 +8273,7 @@
       </c>
       <c r="J138" s="3"/>
     </row>
-    <row r="139" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>68.5</v>
       </c>
@@ -8289,7 +8294,7 @@
       </c>
       <c r="J139" s="3"/>
     </row>
-    <row r="140" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>69</v>
       </c>
@@ -8310,7 +8315,7 @@
       </c>
       <c r="J140" s="3"/>
     </row>
-    <row r="141" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>69.5</v>
       </c>
@@ -8331,7 +8336,7 @@
       </c>
       <c r="J141" s="3"/>
     </row>
-    <row r="142" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>70</v>
       </c>
@@ -8352,7 +8357,7 @@
       </c>
       <c r="J142" s="3"/>
     </row>
-    <row r="143" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>70.5</v>
       </c>
@@ -8373,7 +8378,7 @@
       </c>
       <c r="J143" s="3"/>
     </row>
-    <row r="144" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>71</v>
       </c>
@@ -8394,7 +8399,7 @@
       </c>
       <c r="J144" s="3"/>
     </row>
-    <row r="145" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>71.5</v>
       </c>
@@ -8415,7 +8420,7 @@
       </c>
       <c r="J145" s="3"/>
     </row>
-    <row r="146" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>72</v>
       </c>
@@ -8436,7 +8441,7 @@
       </c>
       <c r="J146" s="3"/>
     </row>
-    <row r="147" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>72.5</v>
       </c>
@@ -8457,7 +8462,7 @@
       </c>
       <c r="J147" s="3"/>
     </row>
-    <row r="148" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>73</v>
       </c>
@@ -8478,7 +8483,7 @@
       </c>
       <c r="J148" s="3"/>
     </row>
-    <row r="149" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>73.5</v>
       </c>
@@ -8499,7 +8504,7 @@
       </c>
       <c r="J149" s="3"/>
     </row>
-    <row r="150" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>74</v>
       </c>
@@ -8520,7 +8525,7 @@
       </c>
       <c r="J150" s="3"/>
     </row>
-    <row r="151" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>74.5</v>
       </c>
@@ -8541,7 +8546,7 @@
       </c>
       <c r="J151" s="3"/>
     </row>
-    <row r="152" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>75</v>
       </c>
@@ -8562,7 +8567,7 @@
       </c>
       <c r="J152" s="3"/>
     </row>
-    <row r="153" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>75.5</v>
       </c>
@@ -8583,7 +8588,7 @@
       </c>
       <c r="J153" s="3"/>
     </row>
-    <row r="154" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>76</v>
       </c>
@@ -8604,7 +8609,7 @@
       </c>
       <c r="J154" s="3"/>
     </row>
-    <row r="155" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>76.5</v>
       </c>
@@ -8625,7 +8630,7 @@
       </c>
       <c r="J155" s="3"/>
     </row>
-    <row r="156" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>77</v>
       </c>
@@ -8646,7 +8651,7 @@
       </c>
       <c r="J156" s="3"/>
     </row>
-    <row r="157" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>77.5</v>
       </c>
@@ -8667,7 +8672,7 @@
       </c>
       <c r="J157" s="3"/>
     </row>
-    <row r="158" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>78</v>
       </c>
@@ -8688,7 +8693,7 @@
       </c>
       <c r="J158" s="3"/>
     </row>
-    <row r="159" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>78.5</v>
       </c>
@@ -8709,7 +8714,7 @@
       </c>
       <c r="J159" s="3"/>
     </row>
-    <row r="160" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>79</v>
       </c>
@@ -8730,7 +8735,7 @@
       </c>
       <c r="J160" s="3"/>
     </row>
-    <row r="161" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>79.5</v>
       </c>
@@ -8751,7 +8756,7 @@
       </c>
       <c r="J161" s="3"/>
     </row>
-    <row r="162" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>80</v>
       </c>
@@ -8772,7 +8777,7 @@
       </c>
       <c r="J162" s="3"/>
     </row>
-    <row r="163" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>80.5</v>
       </c>
@@ -8793,7 +8798,7 @@
       </c>
       <c r="J163" s="3"/>
     </row>
-    <row r="164" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>81</v>
       </c>
@@ -8814,7 +8819,7 @@
       </c>
       <c r="J164" s="3"/>
     </row>
-    <row r="165" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>81.5</v>
       </c>
@@ -8835,7 +8840,7 @@
       </c>
       <c r="J165" s="3"/>
     </row>
-    <row r="166" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>82</v>
       </c>
@@ -8856,7 +8861,7 @@
       </c>
       <c r="J166" s="3"/>
     </row>
-    <row r="167" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>82.5</v>
       </c>
@@ -8877,7 +8882,7 @@
       </c>
       <c r="J167" s="3"/>
     </row>
-    <row r="168" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>83</v>
       </c>
@@ -8898,7 +8903,7 @@
       </c>
       <c r="J168" s="3"/>
     </row>
-    <row r="169" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>83.5</v>
       </c>
@@ -8919,7 +8924,7 @@
       </c>
       <c r="J169" s="3"/>
     </row>
-    <row r="170" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>84</v>
       </c>
@@ -8940,7 +8945,7 @@
       </c>
       <c r="J170" s="3"/>
     </row>
-    <row r="171" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>84.5</v>
       </c>
@@ -8961,7 +8966,7 @@
       </c>
       <c r="J171" s="3"/>
     </row>
-    <row r="172" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>85</v>
       </c>
@@ -8982,7 +8987,7 @@
       </c>
       <c r="J172" s="3"/>
     </row>
-    <row r="173" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>85.5</v>
       </c>
@@ -9003,7 +9008,7 @@
       </c>
       <c r="J173" s="3"/>
     </row>
-    <row r="174" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>86</v>
       </c>
@@ -9024,7 +9029,7 @@
       </c>
       <c r="J174" s="3"/>
     </row>
-    <row r="175" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>86.5</v>
       </c>
@@ -9045,7 +9050,7 @@
       </c>
       <c r="J175" s="3"/>
     </row>
-    <row r="176" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>87</v>
       </c>
@@ -9066,7 +9071,7 @@
       </c>
       <c r="J176" s="3"/>
     </row>
-    <row r="177" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>87.5</v>
       </c>
@@ -9087,7 +9092,7 @@
       </c>
       <c r="J177" s="3"/>
     </row>
-    <row r="178" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>88</v>
       </c>
@@ -9108,7 +9113,7 @@
       </c>
       <c r="J178" s="3"/>
     </row>
-    <row r="179" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>88.5</v>
       </c>
@@ -9129,7 +9134,7 @@
       </c>
       <c r="J179" s="3"/>
     </row>
-    <row r="180" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>89</v>
       </c>
@@ -9150,7 +9155,7 @@
       </c>
       <c r="J180" s="3"/>
     </row>
-    <row r="181" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>89.5</v>
       </c>
@@ -9171,7 +9176,7 @@
       </c>
       <c r="J181" s="3"/>
     </row>
-    <row r="182" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>90</v>
       </c>
@@ -9192,7 +9197,7 @@
       </c>
       <c r="J182" s="3"/>
     </row>
-    <row r="183" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>90.5</v>
       </c>
@@ -9213,7 +9218,7 @@
       </c>
       <c r="J183" s="3"/>
     </row>
-    <row r="184" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>91</v>
       </c>
@@ -9234,7 +9239,7 @@
       </c>
       <c r="J184" s="3"/>
     </row>
-    <row r="185" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>91.5</v>
       </c>
@@ -9255,7 +9260,7 @@
       </c>
       <c r="J185" s="3"/>
     </row>
-    <row r="186" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>92</v>
       </c>
@@ -9276,7 +9281,7 @@
       </c>
       <c r="J186" s="3"/>
     </row>
-    <row r="187" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>92.5</v>
       </c>
@@ -9297,7 +9302,7 @@
       </c>
       <c r="J187" s="3"/>
     </row>
-    <row r="188" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>93</v>
       </c>
@@ -9318,7 +9323,7 @@
       </c>
       <c r="J188" s="3"/>
     </row>
-    <row r="189" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>93.5</v>
       </c>
@@ -9339,7 +9344,7 @@
       </c>
       <c r="J189" s="3"/>
     </row>
-    <row r="190" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>94</v>
       </c>
@@ -9360,7 +9365,7 @@
       </c>
       <c r="J190" s="3"/>
     </row>
-    <row r="191" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>94.5</v>
       </c>
@@ -9381,7 +9386,7 @@
       </c>
       <c r="J191" s="3"/>
     </row>
-    <row r="192" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>95</v>
       </c>
@@ -9402,7 +9407,7 @@
       </c>
       <c r="J192" s="3"/>
     </row>
-    <row r="193" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>95.5</v>
       </c>
@@ -9423,7 +9428,7 @@
       </c>
       <c r="J193" s="3"/>
     </row>
-    <row r="194" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>96</v>
       </c>
@@ -9444,7 +9449,7 @@
       </c>
       <c r="J194" s="3"/>
     </row>
-    <row r="195" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>96.5</v>
       </c>
@@ -9465,7 +9470,7 @@
       </c>
       <c r="J195" s="3"/>
     </row>
-    <row r="196" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>97</v>
       </c>
@@ -9486,7 +9491,7 @@
       </c>
       <c r="J196" s="3"/>
     </row>
-    <row r="197" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>97.5</v>
       </c>
@@ -9507,7 +9512,7 @@
       </c>
       <c r="J197" s="3"/>
     </row>
-    <row r="198" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>98</v>
       </c>
@@ -9528,7 +9533,7 @@
       </c>
       <c r="J198" s="3"/>
     </row>
-    <row r="199" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>98.5</v>
       </c>
@@ -9549,7 +9554,7 @@
       </c>
       <c r="J199" s="3"/>
     </row>
-    <row r="200" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>99</v>
       </c>
@@ -9570,7 +9575,7 @@
       </c>
       <c r="J200" s="3"/>
     </row>
-    <row r="201" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>99.5</v>
       </c>
@@ -9591,7 +9596,7 @@
       </c>
       <c r="J201" s="3"/>
     </row>
-    <row r="202" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>100</v>
       </c>
@@ -9635,7 +9640,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="203" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>100.5</v>
       </c>
@@ -9656,7 +9661,7 @@
       </c>
       <c r="J203" s="3"/>
     </row>
-    <row r="204" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>101</v>
       </c>
@@ -9677,7 +9682,7 @@
       </c>
       <c r="J204" s="3"/>
     </row>
-    <row r="205" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>101.5</v>
       </c>
@@ -9698,7 +9703,7 @@
       </c>
       <c r="J205" s="3"/>
     </row>
-    <row r="206" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>102</v>
       </c>
@@ -9719,7 +9724,7 @@
       </c>
       <c r="J206" s="3"/>
     </row>
-    <row r="207" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>102.5</v>
       </c>
@@ -9740,7 +9745,7 @@
       </c>
       <c r="J207" s="3"/>
     </row>
-    <row r="208" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>103</v>
       </c>
@@ -9761,7 +9766,7 @@
       </c>
       <c r="J208" s="3"/>
     </row>
-    <row r="209" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>103.5</v>
       </c>
@@ -9782,7 +9787,7 @@
       </c>
       <c r="J209" s="3"/>
     </row>
-    <row r="210" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>104</v>
       </c>
@@ -9803,7 +9808,7 @@
       </c>
       <c r="J210" s="3"/>
     </row>
-    <row r="211" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>104.5</v>
       </c>
@@ -9824,7 +9829,7 @@
       </c>
       <c r="J211" s="3"/>
     </row>
-    <row r="212" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>105</v>
       </c>
@@ -9845,7 +9850,7 @@
       </c>
       <c r="J212" s="3"/>
     </row>
-    <row r="213" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>105.5</v>
       </c>
@@ -9866,7 +9871,7 @@
       </c>
       <c r="J213" s="3"/>
     </row>
-    <row r="214" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>106</v>
       </c>
@@ -9887,7 +9892,7 @@
       </c>
       <c r="J214" s="3"/>
     </row>
-    <row r="215" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>106.5</v>
       </c>
@@ -9908,7 +9913,7 @@
       </c>
       <c r="J215" s="3"/>
     </row>
-    <row r="216" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>107</v>
       </c>
@@ -9929,7 +9934,7 @@
       </c>
       <c r="J216" s="3"/>
     </row>
-    <row r="217" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>107.5</v>
       </c>
@@ -9950,7 +9955,7 @@
       </c>
       <c r="J217" s="3"/>
     </row>
-    <row r="218" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>108</v>
       </c>
@@ -9971,7 +9976,7 @@
       </c>
       <c r="J218" s="3"/>
     </row>
-    <row r="219" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>108.5</v>
       </c>
@@ -9992,7 +9997,7 @@
       </c>
       <c r="J219" s="3"/>
     </row>
-    <row r="220" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>109</v>
       </c>
@@ -10013,7 +10018,7 @@
       </c>
       <c r="J220" s="3"/>
     </row>
-    <row r="221" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>109.5</v>
       </c>
@@ -10034,7 +10039,7 @@
       </c>
       <c r="J221" s="3"/>
     </row>
-    <row r="222" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>110</v>
       </c>
@@ -10055,7 +10060,7 @@
       </c>
       <c r="J222" s="3"/>
     </row>
-    <row r="223" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>110.5</v>
       </c>
@@ -10076,7 +10081,7 @@
       </c>
       <c r="J223" s="3"/>
     </row>
-    <row r="224" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>111</v>
       </c>
@@ -10097,7 +10102,7 @@
       </c>
       <c r="J224" s="3"/>
     </row>
-    <row r="225" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>111.5</v>
       </c>
@@ -10118,7 +10123,7 @@
       </c>
       <c r="J225" s="3"/>
     </row>
-    <row r="226" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>112</v>
       </c>
@@ -10139,7 +10144,7 @@
       </c>
       <c r="J226" s="3"/>
     </row>
-    <row r="227" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>112.5</v>
       </c>
@@ -10160,7 +10165,7 @@
       </c>
       <c r="J227" s="3"/>
     </row>
-    <row r="228" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>113</v>
       </c>
@@ -10181,7 +10186,7 @@
       </c>
       <c r="J228" s="3"/>
     </row>
-    <row r="229" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>113.5</v>
       </c>
@@ -10202,7 +10207,7 @@
       </c>
       <c r="J229" s="3"/>
     </row>
-    <row r="230" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>114</v>
       </c>
@@ -10223,7 +10228,7 @@
       </c>
       <c r="J230" s="3"/>
     </row>
-    <row r="231" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>114.5</v>
       </c>
@@ -10244,7 +10249,7 @@
       </c>
       <c r="J231" s="3"/>
     </row>
-    <row r="232" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>115</v>
       </c>
@@ -10265,7 +10270,7 @@
       </c>
       <c r="J232" s="3"/>
     </row>
-    <row r="233" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>115.5</v>
       </c>
@@ -10286,7 +10291,7 @@
       </c>
       <c r="J233" s="3"/>
     </row>
-    <row r="234" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>116</v>
       </c>
@@ -10307,7 +10312,7 @@
       </c>
       <c r="J234" s="3"/>
     </row>
-    <row r="235" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>116.5</v>
       </c>
@@ -10328,7 +10333,7 @@
       </c>
       <c r="J235" s="3"/>
     </row>
-    <row r="236" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>117</v>
       </c>
@@ -10349,7 +10354,7 @@
       </c>
       <c r="J236" s="3"/>
     </row>
-    <row r="237" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>117.5</v>
       </c>
@@ -10370,7 +10375,7 @@
       </c>
       <c r="J237" s="3"/>
     </row>
-    <row r="238" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>118</v>
       </c>
@@ -10391,7 +10396,7 @@
       </c>
       <c r="J238" s="3"/>
     </row>
-    <row r="239" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>118.5</v>
       </c>
@@ -10412,7 +10417,7 @@
       </c>
       <c r="J239" s="3"/>
     </row>
-    <row r="240" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>119</v>
       </c>
@@ -10433,7 +10438,7 @@
       </c>
       <c r="J240" s="3"/>
     </row>
-    <row r="241" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>119.5</v>
       </c>
@@ -10454,7 +10459,7 @@
       </c>
       <c r="J241" s="3"/>
     </row>
-    <row r="242" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>120</v>
       </c>
@@ -10498,290 +10503,290 @@
         <v>4.7060000000000004</v>
       </c>
     </row>
-    <row r="243" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B243" s="2"/>
       <c r="C243" s="1"/>
       <c r="D243" s="2"/>
     </row>
-    <row r="244" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B244" s="2"/>
       <c r="C244" s="1"/>
       <c r="D244" s="2"/>
     </row>
-    <row r="245" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B245" s="2"/>
       <c r="C245" s="1"/>
       <c r="D245" s="2"/>
     </row>
-    <row r="246" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B246" s="2"/>
       <c r="C246" s="1"/>
       <c r="D246" s="2"/>
     </row>
-    <row r="247" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B247" s="2"/>
       <c r="C247" s="1"/>
       <c r="D247" s="2"/>
     </row>
-    <row r="248" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B248" s="2"/>
       <c r="C248" s="1"/>
       <c r="D248" s="2"/>
     </row>
-    <row r="249" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B249" s="2"/>
       <c r="C249" s="1"/>
       <c r="D249" s="2"/>
     </row>
-    <row r="250" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B250" s="2"/>
       <c r="C250" s="1"/>
       <c r="D250" s="2"/>
     </row>
-    <row r="251" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B251" s="2"/>
       <c r="C251" s="1"/>
       <c r="D251" s="2"/>
     </row>
-    <row r="252" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B252" s="2"/>
       <c r="C252" s="1"/>
       <c r="D252" s="2"/>
     </row>
-    <row r="253" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B253" s="2"/>
       <c r="C253" s="1"/>
       <c r="D253" s="2"/>
     </row>
-    <row r="254" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B254" s="2"/>
       <c r="C254" s="1"/>
       <c r="D254" s="2"/>
     </row>
-    <row r="255" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B255" s="2"/>
       <c r="C255" s="1"/>
       <c r="D255" s="2"/>
     </row>
-    <row r="256" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B256" s="2"/>
       <c r="C256" s="1"/>
       <c r="D256" s="2"/>
     </row>
-    <row r="257" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B257" s="2"/>
       <c r="C257" s="1"/>
       <c r="D257" s="2"/>
     </row>
-    <row r="258" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B258" s="2"/>
       <c r="C258" s="1"/>
       <c r="D258" s="2"/>
     </row>
-    <row r="259" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B259" s="2"/>
       <c r="C259" s="1"/>
       <c r="D259" s="2"/>
     </row>
-    <row r="260" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B260" s="2"/>
       <c r="C260" s="1"/>
       <c r="D260" s="2"/>
     </row>
-    <row r="261" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B261" s="2"/>
       <c r="C261" s="1"/>
       <c r="D261" s="2"/>
     </row>
-    <row r="262" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B262" s="2"/>
       <c r="C262" s="1"/>
       <c r="D262" s="2"/>
     </row>
-    <row r="263" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B263" s="2"/>
       <c r="C263" s="1"/>
       <c r="D263" s="2"/>
     </row>
-    <row r="264" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B264" s="2"/>
       <c r="C264" s="1"/>
       <c r="D264" s="2"/>
     </row>
-    <row r="265" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B265" s="2"/>
       <c r="C265" s="1"/>
       <c r="D265" s="2"/>
     </row>
-    <row r="266" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B266" s="2"/>
       <c r="C266" s="1"/>
       <c r="D266" s="2"/>
     </row>
-    <row r="267" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B267" s="2"/>
       <c r="C267" s="1"/>
       <c r="D267" s="2"/>
     </row>
-    <row r="268" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B268" s="2"/>
       <c r="C268" s="1"/>
       <c r="D268" s="2"/>
     </row>
-    <row r="269" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B269" s="2"/>
       <c r="C269" s="1"/>
       <c r="D269" s="2"/>
     </row>
-    <row r="270" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B270" s="2"/>
       <c r="C270" s="1"/>
       <c r="D270" s="2"/>
     </row>
-    <row r="271" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B271" s="2"/>
       <c r="C271" s="1"/>
       <c r="D271" s="2"/>
     </row>
-    <row r="272" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B272" s="2"/>
       <c r="C272" s="1"/>
       <c r="D272" s="2"/>
     </row>
-    <row r="273" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B273" s="2"/>
       <c r="C273" s="1"/>
       <c r="D273" s="2"/>
     </row>
-    <row r="274" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B274" s="2"/>
       <c r="C274" s="1"/>
       <c r="D274" s="2"/>
     </row>
-    <row r="275" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B275" s="2"/>
       <c r="C275" s="1"/>
       <c r="D275" s="2"/>
     </row>
-    <row r="276" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B276" s="2"/>
       <c r="C276" s="1"/>
       <c r="D276" s="2"/>
     </row>
-    <row r="277" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B277" s="2"/>
       <c r="C277" s="1"/>
       <c r="D277" s="2"/>
     </row>
-    <row r="278" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B278" s="2"/>
       <c r="C278" s="1"/>
       <c r="D278" s="2"/>
     </row>
-    <row r="279" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B279" s="2"/>
       <c r="C279" s="1"/>
       <c r="D279" s="2"/>
     </row>
-    <row r="280" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B280" s="2"/>
       <c r="C280" s="1"/>
       <c r="D280" s="2"/>
     </row>
-    <row r="281" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B281" s="2"/>
       <c r="C281" s="1"/>
       <c r="D281" s="2"/>
     </row>
-    <row r="282" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B282" s="2"/>
       <c r="C282" s="1"/>
       <c r="D282" s="2"/>
     </row>
-    <row r="283" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B283" s="2"/>
       <c r="C283" s="1"/>
       <c r="D283" s="2"/>
     </row>
-    <row r="284" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B284" s="2"/>
       <c r="C284" s="1"/>
       <c r="D284" s="2"/>
     </row>
-    <row r="285" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B285" s="2"/>
       <c r="C285" s="1"/>
       <c r="D285" s="2"/>
     </row>
-    <row r="286" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B286" s="2"/>
       <c r="C286" s="1"/>
       <c r="D286" s="2"/>
     </row>
-    <row r="287" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B287" s="2"/>
       <c r="C287" s="1"/>
       <c r="D287" s="2"/>
     </row>
-    <row r="288" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B288" s="2"/>
       <c r="C288" s="1"/>
       <c r="D288" s="2"/>
     </row>
-    <row r="289" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B289" s="2"/>
       <c r="C289" s="1"/>
       <c r="D289" s="2"/>
     </row>
-    <row r="290" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D290" s="2"/>
     </row>
-    <row r="291" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D291" s="2"/>
     </row>
-    <row r="292" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D292" s="2"/>
     </row>
-    <row r="293" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D293" s="2"/>
     </row>
-    <row r="294" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D294" s="2"/>
     </row>
-    <row r="295" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D295" s="2"/>
     </row>
-    <row r="296" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D296" s="2"/>
     </row>
-    <row r="297" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D297" s="2"/>
     </row>
-    <row r="298" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D298" s="2"/>
     </row>
-    <row r="299" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D299" s="2"/>
     </row>
-    <row r="300" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D300" s="2"/>
     </row>
-    <row r="301" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D301" s="2"/>
     </row>
-    <row r="302" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D302" s="2"/>
     </row>
-    <row r="303" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D303" s="2"/>
     </row>
-    <row r="304" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D304" s="2"/>
     </row>
-    <row r="305" spans="4:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D305" s="2"/>
     </row>
-    <row r="306" spans="4:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D306" s="2"/>
     </row>
   </sheetData>
@@ -10792,9 +10797,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D601284-C41C-4456-A5AD-DE6B0EA308E1}">
   <dimension ref="A1:N246"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -10838,7 +10843,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -10882,7 +10887,7 @@
         <v>11.76</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0.5</v>
       </c>
@@ -10902,7 +10907,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -10922,7 +10927,7 @@
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1.5</v>
       </c>
@@ -10942,7 +10947,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -10962,7 +10967,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2.5</v>
       </c>
@@ -10982,7 +10987,7 @@
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -11002,7 +11007,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3.5</v>
       </c>
@@ -11022,7 +11027,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>4</v>
       </c>
@@ -11066,7 +11071,7 @@
         <v>10.39589908</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>4.5</v>
       </c>
@@ -11086,7 +11091,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5</v>
       </c>
@@ -11106,7 +11111,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>5.5</v>
       </c>
@@ -11126,7 +11131,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>6</v>
       </c>
@@ -11146,7 +11151,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>6.5</v>
       </c>
@@ -11166,7 +11171,7 @@
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>7</v>
       </c>
@@ -11186,7 +11191,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>7.5</v>
       </c>
@@ -11206,7 +11211,7 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -11250,7 +11255,7 @@
         <v>12.035942110000001</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>8.5</v>
       </c>
@@ -11270,7 +11275,7 @@
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>9</v>
       </c>
@@ -11290,7 +11295,7 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>9.5</v>
       </c>
@@ -11310,7 +11315,7 @@
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>10</v>
       </c>
@@ -11330,7 +11335,7 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>10.5</v>
       </c>
@@ -11350,7 +11355,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>11</v>
       </c>
@@ -11370,7 +11375,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>11.5</v>
       </c>
@@ -11390,7 +11395,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>12</v>
       </c>
@@ -11410,7 +11415,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>12.5</v>
       </c>
@@ -11430,7 +11435,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>13</v>
       </c>
@@ -11474,7 +11479,7 @@
         <v>8.1759773300000003</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>13.5</v>
       </c>
@@ -11494,7 +11499,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>14</v>
       </c>
@@ -11514,7 +11519,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>14.5</v>
       </c>
@@ -11534,7 +11539,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>15</v>
       </c>
@@ -11554,7 +11559,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>15.5</v>
       </c>
@@ -11574,7 +11579,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>16</v>
       </c>
@@ -11594,7 +11599,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>16.5</v>
       </c>
@@ -11614,7 +11619,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>17</v>
       </c>
@@ -11634,7 +11639,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>17.5</v>
       </c>
@@ -11654,7 +11659,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>18</v>
       </c>
@@ -11698,7 +11703,7 @@
         <v>10.57434372</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>18.5</v>
       </c>
@@ -11718,7 +11723,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>19</v>
       </c>
@@ -11738,7 +11743,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>19.5</v>
       </c>
@@ -11758,7 +11763,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>20</v>
       </c>
@@ -11778,7 +11783,7 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>20.5</v>
       </c>
@@ -11798,7 +11803,7 @@
       </c>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>21</v>
       </c>
@@ -11818,7 +11823,7 @@
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>21.5</v>
       </c>
@@ -11838,7 +11843,7 @@
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>22</v>
       </c>
@@ -11858,7 +11863,7 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>22.5</v>
       </c>
@@ -11878,7 +11883,7 @@
       </c>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>23</v>
       </c>
@@ -11922,7 +11927,7 @@
         <v>7.9746434920000002</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>23.5</v>
       </c>
@@ -11942,7 +11947,7 @@
       </c>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>24</v>
       </c>
@@ -11962,7 +11967,7 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>24.5</v>
       </c>
@@ -11982,7 +11987,7 @@
       </c>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>25</v>
       </c>
@@ -12002,7 +12007,7 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>25.5</v>
       </c>
@@ -12022,7 +12027,7 @@
       </c>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>26</v>
       </c>
@@ -12042,7 +12047,7 @@
       </c>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>26.5</v>
       </c>
@@ -12062,7 +12067,7 @@
       </c>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>27</v>
       </c>
@@ -12082,7 +12087,7 @@
       </c>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>27.5</v>
       </c>
@@ -12102,7 +12107,7 @@
       </c>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>28</v>
       </c>
@@ -12122,7 +12127,7 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>28.5</v>
       </c>
@@ -12142,7 +12147,7 @@
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>29</v>
       </c>
@@ -12162,7 +12167,7 @@
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>29.5</v>
       </c>
@@ -12182,7 +12187,7 @@
       </c>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>30</v>
       </c>
@@ -12202,7 +12207,7 @@
       </c>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>30.5</v>
       </c>
@@ -12222,7 +12227,7 @@
       </c>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>31</v>
       </c>
@@ -12266,7 +12271,7 @@
         <v>9.4558200140000004</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>31.5</v>
       </c>
@@ -12286,7 +12291,7 @@
       </c>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>32</v>
       </c>
@@ -12306,7 +12311,7 @@
       </c>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>32.5</v>
       </c>
@@ -12326,7 +12331,7 @@
       </c>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>33</v>
       </c>
@@ -12346,7 +12351,7 @@
       </c>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>33.5</v>
       </c>
@@ -12366,7 +12371,7 @@
       </c>
       <c r="J69" s="3"/>
     </row>
-    <row r="70" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>34</v>
       </c>
@@ -12386,7 +12391,7 @@
       </c>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>34.5</v>
       </c>
@@ -12406,7 +12411,7 @@
       </c>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>35</v>
       </c>
@@ -12426,7 +12431,7 @@
       </c>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>35.5</v>
       </c>
@@ -12446,7 +12451,7 @@
       </c>
       <c r="J73" s="3"/>
     </row>
-    <row r="74" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>36</v>
       </c>
@@ -12466,7 +12471,7 @@
       </c>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>36.5</v>
       </c>
@@ -12486,7 +12491,7 @@
       </c>
       <c r="J75" s="3"/>
     </row>
-    <row r="76" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>37</v>
       </c>
@@ -12506,7 +12511,7 @@
       </c>
       <c r="J76" s="3"/>
     </row>
-    <row r="77" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>37.5</v>
       </c>
@@ -12526,7 +12531,7 @@
       </c>
       <c r="J77" s="3"/>
     </row>
-    <row r="78" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>38</v>
       </c>
@@ -12546,7 +12551,7 @@
       </c>
       <c r="J78" s="3"/>
     </row>
-    <row r="79" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>38.5</v>
       </c>
@@ -12566,7 +12571,7 @@
       </c>
       <c r="J79" s="3"/>
     </row>
-    <row r="80" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>39</v>
       </c>
@@ -12586,7 +12591,7 @@
       </c>
       <c r="J80" s="3"/>
     </row>
-    <row r="81" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>39.5</v>
       </c>
@@ -12606,7 +12611,7 @@
       </c>
       <c r="J81" s="3"/>
     </row>
-    <row r="82" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>40</v>
       </c>
@@ -12626,7 +12631,7 @@
       </c>
       <c r="J82" s="3"/>
     </row>
-    <row r="83" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>40.5</v>
       </c>
@@ -12646,7 +12651,7 @@
       </c>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>41</v>
       </c>
@@ -12666,7 +12671,7 @@
       </c>
       <c r="J84" s="3"/>
     </row>
-    <row r="85" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>41.5</v>
       </c>
@@ -12686,7 +12691,7 @@
       </c>
       <c r="J85" s="3"/>
     </row>
-    <row r="86" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>42</v>
       </c>
@@ -12706,7 +12711,7 @@
       </c>
       <c r="J86" s="3"/>
     </row>
-    <row r="87" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>42.5</v>
       </c>
@@ -12726,7 +12731,7 @@
       </c>
       <c r="J87" s="3"/>
     </row>
-    <row r="88" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>43</v>
       </c>
@@ -12770,7 +12775,7 @@
         <v>3.089573584</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>43.5</v>
       </c>
@@ -12790,7 +12795,7 @@
       </c>
       <c r="J89" s="3"/>
     </row>
-    <row r="90" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>44</v>
       </c>
@@ -12810,7 +12815,7 @@
       </c>
       <c r="J90" s="3"/>
     </row>
-    <row r="91" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>44.5</v>
       </c>
@@ -12830,7 +12835,7 @@
       </c>
       <c r="J91" s="3"/>
     </row>
-    <row r="92" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45</v>
       </c>
@@ -12850,7 +12855,7 @@
       </c>
       <c r="J92" s="3"/>
     </row>
-    <row r="93" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45.5</v>
       </c>
@@ -12870,7 +12875,7 @@
       </c>
       <c r="J93" s="3"/>
     </row>
-    <row r="94" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46</v>
       </c>
@@ -12890,7 +12895,7 @@
       </c>
       <c r="J94" s="3"/>
     </row>
-    <row r="95" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46.5</v>
       </c>
@@ -12910,7 +12915,7 @@
       </c>
       <c r="J95" s="3"/>
     </row>
-    <row r="96" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>47</v>
       </c>
@@ -12930,7 +12935,7 @@
       </c>
       <c r="J96" s="3"/>
     </row>
-    <row r="97" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>47.5</v>
       </c>
@@ -12950,7 +12955,7 @@
       </c>
       <c r="J97" s="3"/>
     </row>
-    <row r="98" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>48</v>
       </c>
@@ -12970,7 +12975,7 @@
       </c>
       <c r="J98" s="3"/>
     </row>
-    <row r="99" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>48.5</v>
       </c>
@@ -12990,7 +12995,7 @@
       </c>
       <c r="J99" s="3"/>
     </row>
-    <row r="100" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>49</v>
       </c>
@@ -13010,7 +13015,7 @@
       </c>
       <c r="J100" s="3"/>
     </row>
-    <row r="101" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>49.5</v>
       </c>
@@ -13030,7 +13035,7 @@
       </c>
       <c r="J101" s="3"/>
     </row>
-    <row r="102" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>50</v>
       </c>
@@ -13050,7 +13055,7 @@
       </c>
       <c r="J102" s="3"/>
     </row>
-    <row r="103" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>50.5</v>
       </c>
@@ -13070,7 +13075,7 @@
       </c>
       <c r="J103" s="3"/>
     </row>
-    <row r="104" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>51</v>
       </c>
@@ -13090,7 +13095,7 @@
       </c>
       <c r="J104" s="3"/>
     </row>
-    <row r="105" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>51.5</v>
       </c>
@@ -13110,7 +13115,7 @@
       </c>
       <c r="J105" s="3"/>
     </row>
-    <row r="106" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>52</v>
       </c>
@@ -13130,7 +13135,7 @@
       </c>
       <c r="J106" s="3"/>
     </row>
-    <row r="107" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>52.5</v>
       </c>
@@ -13150,7 +13155,7 @@
       </c>
       <c r="J107" s="3"/>
     </row>
-    <row r="108" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>53</v>
       </c>
@@ -13170,7 +13175,7 @@
       </c>
       <c r="J108" s="3"/>
     </row>
-    <row r="109" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>53.5</v>
       </c>
@@ -13190,7 +13195,7 @@
       </c>
       <c r="J109" s="3"/>
     </row>
-    <row r="110" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>54</v>
       </c>
@@ -13210,7 +13215,7 @@
       </c>
       <c r="J110" s="3"/>
     </row>
-    <row r="111" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>54.5</v>
       </c>
@@ -13230,7 +13235,7 @@
       </c>
       <c r="J111" s="3"/>
     </row>
-    <row r="112" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>55</v>
       </c>
@@ -13250,7 +13255,7 @@
       </c>
       <c r="J112" s="3"/>
     </row>
-    <row r="113" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>55.5</v>
       </c>
@@ -13270,7 +13275,7 @@
       </c>
       <c r="J113" s="3"/>
     </row>
-    <row r="114" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>56</v>
       </c>
@@ -13290,7 +13295,7 @@
       </c>
       <c r="J114" s="3"/>
     </row>
-    <row r="115" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>56.5</v>
       </c>
@@ -13310,7 +13315,7 @@
       </c>
       <c r="J115" s="3"/>
     </row>
-    <row r="116" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>57</v>
       </c>
@@ -13330,7 +13335,7 @@
       </c>
       <c r="J116" s="3"/>
     </row>
-    <row r="117" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>57.5</v>
       </c>
@@ -13350,7 +13355,7 @@
       </c>
       <c r="J117" s="3"/>
     </row>
-    <row r="118" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>58</v>
       </c>
@@ -13370,7 +13375,7 @@
       </c>
       <c r="J118" s="3"/>
     </row>
-    <row r="119" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>58.5</v>
       </c>
@@ -13390,7 +13395,7 @@
       </c>
       <c r="J119" s="3"/>
     </row>
-    <row r="120" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>59</v>
       </c>
@@ -13410,7 +13415,7 @@
       </c>
       <c r="J120" s="3"/>
     </row>
-    <row r="121" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>59.5</v>
       </c>
@@ -13430,7 +13435,7 @@
       </c>
       <c r="J121" s="3"/>
     </row>
-    <row r="122" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>60</v>
       </c>
@@ -13474,7 +13479,7 @@
         <v>4.8133078640000004</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>60.5</v>
       </c>
@@ -13494,7 +13499,7 @@
       </c>
       <c r="J123" s="3"/>
     </row>
-    <row r="124" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>61</v>
       </c>
@@ -13514,7 +13519,7 @@
       </c>
       <c r="J124" s="3"/>
     </row>
-    <row r="125" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>61.5</v>
       </c>
@@ -13534,7 +13539,7 @@
       </c>
       <c r="J125" s="3"/>
     </row>
-    <row r="126" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>62</v>
       </c>
@@ -13554,7 +13559,7 @@
       </c>
       <c r="J126" s="3"/>
     </row>
-    <row r="127" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>62.5</v>
       </c>
@@ -13574,7 +13579,7 @@
       </c>
       <c r="J127" s="3"/>
     </row>
-    <row r="128" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>63</v>
       </c>
@@ -13594,7 +13599,7 @@
       </c>
       <c r="J128" s="3"/>
     </row>
-    <row r="129" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>63.5</v>
       </c>
@@ -13614,7 +13619,7 @@
       </c>
       <c r="J129" s="3"/>
     </row>
-    <row r="130" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>64</v>
       </c>
@@ -13634,7 +13639,7 @@
       </c>
       <c r="J130" s="3"/>
     </row>
-    <row r="131" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>64.5</v>
       </c>
@@ -13654,7 +13659,7 @@
       </c>
       <c r="J131" s="3"/>
     </row>
-    <row r="132" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>65</v>
       </c>
@@ -13674,7 +13679,7 @@
       </c>
       <c r="J132" s="3"/>
     </row>
-    <row r="133" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>65.5</v>
       </c>
@@ -13694,7 +13699,7 @@
       </c>
       <c r="J133" s="3"/>
     </row>
-    <row r="134" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>66</v>
       </c>
@@ -13714,7 +13719,7 @@
       </c>
       <c r="J134" s="3"/>
     </row>
-    <row r="135" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>66.5</v>
       </c>
@@ -13734,7 +13739,7 @@
       </c>
       <c r="J135" s="3"/>
     </row>
-    <row r="136" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>67</v>
       </c>
@@ -13754,7 +13759,7 @@
       </c>
       <c r="J136" s="3"/>
     </row>
-    <row r="137" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>67.5</v>
       </c>
@@ -13774,7 +13779,7 @@
       </c>
       <c r="J137" s="3"/>
     </row>
-    <row r="138" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>68</v>
       </c>
@@ -13794,7 +13799,7 @@
       </c>
       <c r="J138" s="3"/>
     </row>
-    <row r="139" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>68.5</v>
       </c>
@@ -13814,7 +13819,7 @@
       </c>
       <c r="J139" s="3"/>
     </row>
-    <row r="140" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>69</v>
       </c>
@@ -13834,7 +13839,7 @@
       </c>
       <c r="J140" s="3"/>
     </row>
-    <row r="141" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>69.5</v>
       </c>
@@ -13854,7 +13859,7 @@
       </c>
       <c r="J141" s="3"/>
     </row>
-    <row r="142" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>70</v>
       </c>
@@ -13874,7 +13879,7 @@
       </c>
       <c r="J142" s="3"/>
     </row>
-    <row r="143" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>70.5</v>
       </c>
@@ -13894,7 +13899,7 @@
       </c>
       <c r="J143" s="3"/>
     </row>
-    <row r="144" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>71</v>
       </c>
@@ -13914,7 +13919,7 @@
       </c>
       <c r="J144" s="3"/>
     </row>
-    <row r="145" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>71.5</v>
       </c>
@@ -13934,7 +13939,7 @@
       </c>
       <c r="J145" s="3"/>
     </row>
-    <row r="146" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>72</v>
       </c>
@@ -13954,7 +13959,7 @@
       </c>
       <c r="J146" s="3"/>
     </row>
-    <row r="147" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>72.5</v>
       </c>
@@ -13974,7 +13979,7 @@
       </c>
       <c r="J147" s="3"/>
     </row>
-    <row r="148" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>73</v>
       </c>
@@ -13994,7 +13999,7 @@
       </c>
       <c r="J148" s="3"/>
     </row>
-    <row r="149" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>73.5</v>
       </c>
@@ -14014,7 +14019,7 @@
       </c>
       <c r="J149" s="3"/>
     </row>
-    <row r="150" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>74</v>
       </c>
@@ -14034,7 +14039,7 @@
       </c>
       <c r="J150" s="3"/>
     </row>
-    <row r="151" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>74.5</v>
       </c>
@@ -14054,7 +14059,7 @@
       </c>
       <c r="J151" s="3"/>
     </row>
-    <row r="152" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>75</v>
       </c>
@@ -14074,7 +14079,7 @@
       </c>
       <c r="J152" s="3"/>
     </row>
-    <row r="153" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>75.5</v>
       </c>
@@ -14094,7 +14099,7 @@
       </c>
       <c r="J153" s="3"/>
     </row>
-    <row r="154" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>76</v>
       </c>
@@ -14114,7 +14119,7 @@
       </c>
       <c r="J154" s="3"/>
     </row>
-    <row r="155" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>76.5</v>
       </c>
@@ -14134,7 +14139,7 @@
       </c>
       <c r="J155" s="3"/>
     </row>
-    <row r="156" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>77</v>
       </c>
@@ -14154,7 +14159,7 @@
       </c>
       <c r="J156" s="3"/>
     </row>
-    <row r="157" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>77.5</v>
       </c>
@@ -14174,7 +14179,7 @@
       </c>
       <c r="J157" s="3"/>
     </row>
-    <row r="158" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>78</v>
       </c>
@@ -14194,7 +14199,7 @@
       </c>
       <c r="J158" s="3"/>
     </row>
-    <row r="159" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>78.5</v>
       </c>
@@ -14214,7 +14219,7 @@
       </c>
       <c r="J159" s="3"/>
     </row>
-    <row r="160" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>79</v>
       </c>
@@ -14234,7 +14239,7 @@
       </c>
       <c r="J160" s="3"/>
     </row>
-    <row r="161" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>79.5</v>
       </c>
@@ -14254,7 +14259,7 @@
       </c>
       <c r="J161" s="3"/>
     </row>
-    <row r="162" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>80</v>
       </c>
@@ -14274,7 +14279,7 @@
       </c>
       <c r="J162" s="3"/>
     </row>
-    <row r="163" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>80.5</v>
       </c>
@@ -14294,7 +14299,7 @@
       </c>
       <c r="J163" s="3"/>
     </row>
-    <row r="164" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>81</v>
       </c>
@@ -14314,7 +14319,7 @@
       </c>
       <c r="J164" s="3"/>
     </row>
-    <row r="165" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>81.5</v>
       </c>
@@ -14334,7 +14339,7 @@
       </c>
       <c r="J165" s="3"/>
     </row>
-    <row r="166" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>82</v>
       </c>
@@ -14354,7 +14359,7 @@
       </c>
       <c r="J166" s="3"/>
     </row>
-    <row r="167" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>82.5</v>
       </c>
@@ -14374,7 +14379,7 @@
       </c>
       <c r="J167" s="3"/>
     </row>
-    <row r="168" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>83</v>
       </c>
@@ -14394,7 +14399,7 @@
       </c>
       <c r="J168" s="3"/>
     </row>
-    <row r="169" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>83.5</v>
       </c>
@@ -14414,7 +14419,7 @@
       </c>
       <c r="J169" s="3"/>
     </row>
-    <row r="170" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>84</v>
       </c>
@@ -14434,7 +14439,7 @@
       </c>
       <c r="J170" s="3"/>
     </row>
-    <row r="171" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>84.5</v>
       </c>
@@ -14454,7 +14459,7 @@
       </c>
       <c r="J171" s="3"/>
     </row>
-    <row r="172" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>85</v>
       </c>
@@ -14474,7 +14479,7 @@
       </c>
       <c r="J172" s="3"/>
     </row>
-    <row r="173" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>85.5</v>
       </c>
@@ -14494,7 +14499,7 @@
       </c>
       <c r="J173" s="3"/>
     </row>
-    <row r="174" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>86</v>
       </c>
@@ -14514,7 +14519,7 @@
       </c>
       <c r="J174" s="3"/>
     </row>
-    <row r="175" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>86.5</v>
       </c>
@@ -14534,7 +14539,7 @@
       </c>
       <c r="J175" s="3"/>
     </row>
-    <row r="176" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>87</v>
       </c>
@@ -14554,7 +14559,7 @@
       </c>
       <c r="J176" s="3"/>
     </row>
-    <row r="177" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>87.5</v>
       </c>
@@ -14574,7 +14579,7 @@
       </c>
       <c r="J177" s="3"/>
     </row>
-    <row r="178" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>88</v>
       </c>
@@ -14594,7 +14599,7 @@
       </c>
       <c r="J178" s="3"/>
     </row>
-    <row r="179" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>88.5</v>
       </c>
@@ -14614,7 +14619,7 @@
       </c>
       <c r="J179" s="3"/>
     </row>
-    <row r="180" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>89</v>
       </c>
@@ -14634,7 +14639,7 @@
       </c>
       <c r="J180" s="3"/>
     </row>
-    <row r="181" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>89.5</v>
       </c>
@@ -14654,7 +14659,7 @@
       </c>
       <c r="J181" s="3"/>
     </row>
-    <row r="182" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>90</v>
       </c>
@@ -14674,7 +14679,7 @@
       </c>
       <c r="J182" s="3"/>
     </row>
-    <row r="183" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>90.5</v>
       </c>
@@ -14694,7 +14699,7 @@
       </c>
       <c r="J183" s="3"/>
     </row>
-    <row r="184" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>91</v>
       </c>
@@ -14714,7 +14719,7 @@
       </c>
       <c r="J184" s="3"/>
     </row>
-    <row r="185" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>91.5</v>
       </c>
@@ -14734,7 +14739,7 @@
       </c>
       <c r="J185" s="3"/>
     </row>
-    <row r="186" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>92</v>
       </c>
@@ -14754,7 +14759,7 @@
       </c>
       <c r="J186" s="3"/>
     </row>
-    <row r="187" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>92.5</v>
       </c>
@@ -14774,7 +14779,7 @@
       </c>
       <c r="J187" s="3"/>
     </row>
-    <row r="188" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>93</v>
       </c>
@@ -14794,7 +14799,7 @@
       </c>
       <c r="J188" s="3"/>
     </row>
-    <row r="189" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>93.5</v>
       </c>
@@ -14814,7 +14819,7 @@
       </c>
       <c r="J189" s="3"/>
     </row>
-    <row r="190" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>94</v>
       </c>
@@ -14834,7 +14839,7 @@
       </c>
       <c r="J190" s="3"/>
     </row>
-    <row r="191" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>94.5</v>
       </c>
@@ -14854,7 +14859,7 @@
       </c>
       <c r="J191" s="3"/>
     </row>
-    <row r="192" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>95</v>
       </c>
@@ -14874,7 +14879,7 @@
       </c>
       <c r="J192" s="3"/>
     </row>
-    <row r="193" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>95.5</v>
       </c>
@@ -14894,7 +14899,7 @@
       </c>
       <c r="J193" s="3"/>
     </row>
-    <row r="194" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>96</v>
       </c>
@@ -14914,7 +14919,7 @@
       </c>
       <c r="J194" s="3"/>
     </row>
-    <row r="195" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>96.5</v>
       </c>
@@ -14934,7 +14939,7 @@
       </c>
       <c r="J195" s="3"/>
     </row>
-    <row r="196" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>97</v>
       </c>
@@ -14954,7 +14959,7 @@
       </c>
       <c r="J196" s="3"/>
     </row>
-    <row r="197" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>97.5</v>
       </c>
@@ -14974,7 +14979,7 @@
       </c>
       <c r="J197" s="3"/>
     </row>
-    <row r="198" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>98</v>
       </c>
@@ -14994,7 +14999,7 @@
       </c>
       <c r="J198" s="3"/>
     </row>
-    <row r="199" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>98.5</v>
       </c>
@@ -15014,7 +15019,7 @@
       </c>
       <c r="J199" s="3"/>
     </row>
-    <row r="200" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>99</v>
       </c>
@@ -15034,7 +15039,7 @@
       </c>
       <c r="J200" s="3"/>
     </row>
-    <row r="201" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>99.5</v>
       </c>
@@ -15054,7 +15059,7 @@
       </c>
       <c r="J201" s="3"/>
     </row>
-    <row r="202" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>100</v>
       </c>
@@ -15098,7 +15103,7 @@
         <v>4.24780742</v>
       </c>
     </row>
-    <row r="203" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>100.5</v>
       </c>
@@ -15118,7 +15123,7 @@
       </c>
       <c r="J203" s="3"/>
     </row>
-    <row r="204" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>101</v>
       </c>
@@ -15138,7 +15143,7 @@
       </c>
       <c r="J204" s="3"/>
     </row>
-    <row r="205" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>101.5</v>
       </c>
@@ -15158,7 +15163,7 @@
       </c>
       <c r="J205" s="3"/>
     </row>
-    <row r="206" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>102</v>
       </c>
@@ -15178,7 +15183,7 @@
       </c>
       <c r="J206" s="3"/>
     </row>
-    <row r="207" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>102.5</v>
       </c>
@@ -15198,7 +15203,7 @@
       </c>
       <c r="J207" s="3"/>
     </row>
-    <row r="208" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>103</v>
       </c>
@@ -15218,7 +15223,7 @@
       </c>
       <c r="J208" s="3"/>
     </row>
-    <row r="209" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>103.5</v>
       </c>
@@ -15238,7 +15243,7 @@
       </c>
       <c r="J209" s="3"/>
     </row>
-    <row r="210" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>104</v>
       </c>
@@ -15258,7 +15263,7 @@
       </c>
       <c r="J210" s="3"/>
     </row>
-    <row r="211" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>104.5</v>
       </c>
@@ -15278,7 +15283,7 @@
       </c>
       <c r="J211" s="3"/>
     </row>
-    <row r="212" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>105</v>
       </c>
@@ -15298,7 +15303,7 @@
       </c>
       <c r="J212" s="3"/>
     </row>
-    <row r="213" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>105.5</v>
       </c>
@@ -15318,7 +15323,7 @@
       </c>
       <c r="J213" s="3"/>
     </row>
-    <row r="214" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>106</v>
       </c>
@@ -15338,7 +15343,7 @@
       </c>
       <c r="J214" s="3"/>
     </row>
-    <row r="215" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>106.5</v>
       </c>
@@ -15358,7 +15363,7 @@
       </c>
       <c r="J215" s="3"/>
     </row>
-    <row r="216" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>107</v>
       </c>
@@ -15378,7 +15383,7 @@
       </c>
       <c r="J216" s="3"/>
     </row>
-    <row r="217" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>107.5</v>
       </c>
@@ -15398,7 +15403,7 @@
       </c>
       <c r="J217" s="3"/>
     </row>
-    <row r="218" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>108</v>
       </c>
@@ -15418,7 +15423,7 @@
       </c>
       <c r="J218" s="3"/>
     </row>
-    <row r="219" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>108.5</v>
       </c>
@@ -15438,7 +15443,7 @@
       </c>
       <c r="J219" s="3"/>
     </row>
-    <row r="220" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>109</v>
       </c>
@@ -15458,7 +15463,7 @@
       </c>
       <c r="J220" s="3"/>
     </row>
-    <row r="221" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>109.5</v>
       </c>
@@ -15478,7 +15483,7 @@
       </c>
       <c r="J221" s="3"/>
     </row>
-    <row r="222" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>110</v>
       </c>
@@ -15498,7 +15503,7 @@
       </c>
       <c r="J222" s="3"/>
     </row>
-    <row r="223" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>110.5</v>
       </c>
@@ -15518,7 +15523,7 @@
       </c>
       <c r="J223" s="3"/>
     </row>
-    <row r="224" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>111</v>
       </c>
@@ -15538,7 +15543,7 @@
       </c>
       <c r="J224" s="3"/>
     </row>
-    <row r="225" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>111.5</v>
       </c>
@@ -15558,7 +15563,7 @@
       </c>
       <c r="J225" s="3"/>
     </row>
-    <row r="226" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>112</v>
       </c>
@@ -15578,7 +15583,7 @@
       </c>
       <c r="J226" s="3"/>
     </row>
-    <row r="227" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>112.5</v>
       </c>
@@ -15598,7 +15603,7 @@
       </c>
       <c r="J227" s="3"/>
     </row>
-    <row r="228" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>113</v>
       </c>
@@ -15618,7 +15623,7 @@
       </c>
       <c r="J228" s="3"/>
     </row>
-    <row r="229" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>113.5</v>
       </c>
@@ -15638,7 +15643,7 @@
       </c>
       <c r="J229" s="3"/>
     </row>
-    <row r="230" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>114</v>
       </c>
@@ -15658,7 +15663,7 @@
       </c>
       <c r="J230" s="3"/>
     </row>
-    <row r="231" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>114.5</v>
       </c>
@@ -15678,7 +15683,7 @@
       </c>
       <c r="J231" s="3"/>
     </row>
-    <row r="232" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>115</v>
       </c>
@@ -15698,7 +15703,7 @@
       </c>
       <c r="J232" s="3"/>
     </row>
-    <row r="233" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>115.5</v>
       </c>
@@ -15718,7 +15723,7 @@
       </c>
       <c r="J233" s="3"/>
     </row>
-    <row r="234" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>116</v>
       </c>
@@ -15738,7 +15743,7 @@
       </c>
       <c r="J234" s="3"/>
     </row>
-    <row r="235" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>116.5</v>
       </c>
@@ -15758,7 +15763,7 @@
       </c>
       <c r="J235" s="3"/>
     </row>
-    <row r="236" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>117</v>
       </c>
@@ -15778,7 +15783,7 @@
       </c>
       <c r="J236" s="3"/>
     </row>
-    <row r="237" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>117.5</v>
       </c>
@@ -15798,7 +15803,7 @@
       </c>
       <c r="J237" s="3"/>
     </row>
-    <row r="238" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>118</v>
       </c>
@@ -15818,7 +15823,7 @@
       </c>
       <c r="J238" s="3"/>
     </row>
-    <row r="239" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>118.5</v>
       </c>
@@ -15838,7 +15843,7 @@
       </c>
       <c r="J239" s="3"/>
     </row>
-    <row r="240" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>119</v>
       </c>
@@ -15858,7 +15863,7 @@
       </c>
       <c r="J240" s="3"/>
     </row>
-    <row r="241" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>119.5</v>
       </c>
@@ -15878,7 +15883,7 @@
       </c>
       <c r="J241" s="3"/>
     </row>
-    <row r="242" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>120</v>
       </c>
@@ -15922,23 +15927,23 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="243" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B243" s="2"/>
       <c r="C243" s="1"/>
       <c r="D243" s="2"/>
       <c r="I243" s="3"/>
     </row>
-    <row r="244" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B244" s="2"/>
       <c r="C244" s="1"/>
       <c r="D244" s="2"/>
     </row>
-    <row r="245" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B245" s="2"/>
       <c r="C245" s="1"/>
       <c r="D245" s="2"/>
     </row>
-    <row r="246" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D246" s="2"/>
     </row>
   </sheetData>
@@ -15949,9 +15954,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEF14900-1058-4EEF-9BB9-01AFEB47CC28}">
   <dimension ref="A1:L242"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -15989,7 +15994,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -16027,7 +16032,7 @@
         <v>10.46</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0.5</v>
       </c>
@@ -16044,7 +16049,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -16061,7 +16066,7 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1.5</v>
       </c>
@@ -16078,7 +16083,7 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -16095,7 +16100,7 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2.5</v>
       </c>
@@ -16112,7 +16117,7 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -16129,7 +16134,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3.5</v>
       </c>
@@ -16146,7 +16151,7 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>4</v>
       </c>
@@ -16184,7 +16189,7 @@
         <v>9.84</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>4.5</v>
       </c>
@@ -16201,7 +16206,7 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5</v>
       </c>
@@ -16218,7 +16223,7 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>5.5</v>
       </c>
@@ -16235,7 +16240,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>6</v>
       </c>
@@ -16252,7 +16257,7 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>6.5</v>
       </c>
@@ -16269,7 +16274,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>7</v>
       </c>
@@ -16286,7 +16291,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>7.5</v>
       </c>
@@ -16303,7 +16308,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>8</v>
       </c>
@@ -16341,7 +16346,7 @@
         <v>9.44</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>8.5</v>
       </c>
@@ -16358,7 +16363,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>9</v>
       </c>
@@ -16375,7 +16380,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>9.5</v>
       </c>
@@ -16392,7 +16397,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>10</v>
       </c>
@@ -16409,7 +16414,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>10.5</v>
       </c>
@@ -16426,7 +16431,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>11</v>
       </c>
@@ -16443,7 +16448,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>11.5</v>
       </c>
@@ -16460,7 +16465,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>12</v>
       </c>
@@ -16477,7 +16482,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>12.5</v>
       </c>
@@ -16494,7 +16499,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>13</v>
       </c>
@@ -16532,7 +16537,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>13.5</v>
       </c>
@@ -16549,7 +16554,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>14</v>
       </c>
@@ -16566,7 +16571,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>14.5</v>
       </c>
@@ -16583,7 +16588,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>15</v>
       </c>
@@ -16600,7 +16605,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>15.5</v>
       </c>
@@ -16617,7 +16622,7 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>16</v>
       </c>
@@ -16634,7 +16639,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>16.5</v>
       </c>
@@ -16651,7 +16656,7 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>17</v>
       </c>
@@ -16668,7 +16673,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>17.5</v>
       </c>
@@ -16685,7 +16690,7 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>18</v>
       </c>
@@ -16723,7 +16728,7 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>18.5</v>
       </c>
@@ -16740,7 +16745,7 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>19</v>
       </c>
@@ -16757,7 +16762,7 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>19.5</v>
       </c>
@@ -16774,7 +16779,7 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>20</v>
       </c>
@@ -16791,7 +16796,7 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>20.5</v>
       </c>
@@ -16808,7 +16813,7 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>21</v>
       </c>
@@ -16825,7 +16830,7 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>21.5</v>
       </c>
@@ -16842,7 +16847,7 @@
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>22</v>
       </c>
@@ -16859,7 +16864,7 @@
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>22.5</v>
       </c>
@@ -16876,7 +16881,7 @@
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>23</v>
       </c>
@@ -16914,7 +16919,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>23.5</v>
       </c>
@@ -16931,7 +16936,7 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>24</v>
       </c>
@@ -16948,7 +16953,7 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>24.5</v>
       </c>
@@ -16965,7 +16970,7 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>25</v>
       </c>
@@ -16982,7 +16987,7 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>25.5</v>
       </c>
@@ -16999,7 +17004,7 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>26</v>
       </c>
@@ -17016,7 +17021,7 @@
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>26.5</v>
       </c>
@@ -17033,7 +17038,7 @@
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>27</v>
       </c>
@@ -17050,7 +17055,7 @@
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>27.5</v>
       </c>
@@ -17067,7 +17072,7 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>28</v>
       </c>
@@ -17084,7 +17089,7 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>28.5</v>
       </c>
@@ -17101,7 +17106,7 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>29</v>
       </c>
@@ -17118,7 +17123,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>29.5</v>
       </c>
@@ -17135,7 +17140,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>30</v>
       </c>
@@ -17152,7 +17157,7 @@
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>30.5</v>
       </c>
@@ -17169,7 +17174,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>31</v>
       </c>
@@ -17207,7 +17212,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>31.5</v>
       </c>
@@ -17224,7 +17229,7 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
     </row>
-    <row r="66" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>32</v>
       </c>
@@ -17241,7 +17246,7 @@
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>32.5</v>
       </c>
@@ -17258,7 +17263,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>33</v>
       </c>
@@ -17275,7 +17280,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>33.5</v>
       </c>
@@ -17292,7 +17297,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>34</v>
       </c>
@@ -17309,7 +17314,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>34.5</v>
       </c>
@@ -17326,7 +17331,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>35</v>
       </c>
@@ -17343,7 +17348,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>35.5</v>
       </c>
@@ -17360,7 +17365,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>36</v>
       </c>
@@ -17377,7 +17382,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>36.5</v>
       </c>
@@ -17394,7 +17399,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>37</v>
       </c>
@@ -17411,7 +17416,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>37.5</v>
       </c>
@@ -17428,7 +17433,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>38</v>
       </c>
@@ -17445,7 +17450,7 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>38.5</v>
       </c>
@@ -17462,7 +17467,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>39</v>
       </c>
@@ -17479,7 +17484,7 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>39.5</v>
       </c>
@@ -17496,7 +17501,7 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>40</v>
       </c>
@@ -17513,7 +17518,7 @@
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>40.5</v>
       </c>
@@ -17530,7 +17535,7 @@
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>41</v>
       </c>
@@ -17547,7 +17552,7 @@
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>41.5</v>
       </c>
@@ -17564,7 +17569,7 @@
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>42</v>
       </c>
@@ -17581,7 +17586,7 @@
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>42.5</v>
       </c>
@@ -17598,7 +17603,7 @@
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>43</v>
       </c>
@@ -17636,7 +17641,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>43.5</v>
       </c>
@@ -17653,7 +17658,7 @@
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>44</v>
       </c>
@@ -17670,7 +17675,7 @@
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>44.5</v>
       </c>
@@ -17687,7 +17692,7 @@
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45</v>
       </c>
@@ -17704,7 +17709,7 @@
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45.5</v>
       </c>
@@ -17721,7 +17726,7 @@
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46</v>
       </c>
@@ -17738,7 +17743,7 @@
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
     </row>
-    <row r="95" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46.5</v>
       </c>
@@ -17755,7 +17760,7 @@
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>47</v>
       </c>
@@ -17772,7 +17777,7 @@
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
     </row>
-    <row r="97" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>47.5</v>
       </c>
@@ -17789,7 +17794,7 @@
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
     </row>
-    <row r="98" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>48</v>
       </c>
@@ -17806,7 +17811,7 @@
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
     </row>
-    <row r="99" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>48.5</v>
       </c>
@@ -17823,7 +17828,7 @@
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
     </row>
-    <row r="100" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>49</v>
       </c>
@@ -17840,7 +17845,7 @@
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
     </row>
-    <row r="101" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>49.5</v>
       </c>
@@ -17857,7 +17862,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>50</v>
       </c>
@@ -17874,7 +17879,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>50.5</v>
       </c>
@@ -17891,7 +17896,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>51</v>
       </c>
@@ -17908,7 +17913,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>51.5</v>
       </c>
@@ -17925,7 +17930,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>52</v>
       </c>
@@ -17942,7 +17947,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>52.5</v>
       </c>
@@ -17959,7 +17964,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>53</v>
       </c>
@@ -17976,7 +17981,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>53.5</v>
       </c>
@@ -17993,7 +17998,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>54</v>
       </c>
@@ -18010,7 +18015,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>54.5</v>
       </c>
@@ -18027,7 +18032,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>55</v>
       </c>
@@ -18044,7 +18049,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>55.5</v>
       </c>
@@ -18061,7 +18066,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>56</v>
       </c>
@@ -18078,7 +18083,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>56.5</v>
       </c>
@@ -18095,7 +18100,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>57</v>
       </c>
@@ -18112,7 +18117,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>57.5</v>
       </c>
@@ -18129,7 +18134,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>58</v>
       </c>
@@ -18146,7 +18151,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>58.5</v>
       </c>
@@ -18163,7 +18168,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>59</v>
       </c>
@@ -18180,7 +18185,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>59.5</v>
       </c>
@@ -18197,7 +18202,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>60</v>
       </c>
@@ -18235,7 +18240,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>60.5</v>
       </c>
@@ -18252,7 +18257,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>61</v>
       </c>
@@ -18269,7 +18274,7 @@
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
     </row>
-    <row r="125" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>61.5</v>
       </c>
@@ -18286,7 +18291,7 @@
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
     </row>
-    <row r="126" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>62</v>
       </c>
@@ -18303,7 +18308,7 @@
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
     </row>
-    <row r="127" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>62.5</v>
       </c>
@@ -18320,7 +18325,7 @@
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
     </row>
-    <row r="128" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>63</v>
       </c>
@@ -18337,7 +18342,7 @@
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
     </row>
-    <row r="129" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>63.5</v>
       </c>
@@ -18354,7 +18359,7 @@
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
     </row>
-    <row r="130" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>64</v>
       </c>
@@ -18371,7 +18376,7 @@
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
     </row>
-    <row r="131" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>64.5</v>
       </c>
@@ -18388,7 +18393,7 @@
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
     </row>
-    <row r="132" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>65</v>
       </c>
@@ -18405,7 +18410,7 @@
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
     </row>
-    <row r="133" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>65.5</v>
       </c>
@@ -18422,7 +18427,7 @@
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
     </row>
-    <row r="134" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>66</v>
       </c>
@@ -18439,7 +18444,7 @@
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
     </row>
-    <row r="135" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>66.5</v>
       </c>
@@ -18456,7 +18461,7 @@
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
     </row>
-    <row r="136" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>67</v>
       </c>
@@ -18473,7 +18478,7 @@
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
     </row>
-    <row r="137" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>67.5</v>
       </c>
@@ -18490,7 +18495,7 @@
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
     </row>
-    <row r="138" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>68</v>
       </c>
@@ -18507,7 +18512,7 @@
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
     </row>
-    <row r="139" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>68.5</v>
       </c>
@@ -18524,7 +18529,7 @@
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
     </row>
-    <row r="140" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>69</v>
       </c>
@@ -18541,7 +18546,7 @@
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
     </row>
-    <row r="141" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>69.5</v>
       </c>
@@ -18558,7 +18563,7 @@
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
     </row>
-    <row r="142" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>70</v>
       </c>
@@ -18575,7 +18580,7 @@
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
     </row>
-    <row r="143" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>70.5</v>
       </c>
@@ -18592,7 +18597,7 @@
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
     </row>
-    <row r="144" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>71</v>
       </c>
@@ -18609,7 +18614,7 @@
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
     </row>
-    <row r="145" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>71.5</v>
       </c>
@@ -18626,7 +18631,7 @@
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
     </row>
-    <row r="146" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>72</v>
       </c>
@@ -18643,7 +18648,7 @@
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
     </row>
-    <row r="147" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>72.5</v>
       </c>
@@ -18660,7 +18665,7 @@
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
     </row>
-    <row r="148" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>73</v>
       </c>
@@ -18677,7 +18682,7 @@
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
     </row>
-    <row r="149" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>73.5</v>
       </c>
@@ -18694,7 +18699,7 @@
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
     </row>
-    <row r="150" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>74</v>
       </c>
@@ -18711,7 +18716,7 @@
       <c r="F150" s="1"/>
       <c r="G150" s="1"/>
     </row>
-    <row r="151" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>74.5</v>
       </c>
@@ -18728,7 +18733,7 @@
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
     </row>
-    <row r="152" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>75</v>
       </c>
@@ -18745,7 +18750,7 @@
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
     </row>
-    <row r="153" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>75.5</v>
       </c>
@@ -18762,7 +18767,7 @@
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
     </row>
-    <row r="154" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>76</v>
       </c>
@@ -18779,7 +18784,7 @@
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
     </row>
-    <row r="155" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>76.5</v>
       </c>
@@ -18796,7 +18801,7 @@
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
     </row>
-    <row r="156" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>77</v>
       </c>
@@ -18813,7 +18818,7 @@
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
     </row>
-    <row r="157" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>77.5</v>
       </c>
@@ -18830,7 +18835,7 @@
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
     </row>
-    <row r="158" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>78</v>
       </c>
@@ -18847,7 +18852,7 @@
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
     </row>
-    <row r="159" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>78.5</v>
       </c>
@@ -18864,7 +18869,7 @@
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
     </row>
-    <row r="160" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>79</v>
       </c>
@@ -18881,7 +18886,7 @@
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
     </row>
-    <row r="161" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>79.5</v>
       </c>
@@ -18898,7 +18903,7 @@
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
     </row>
-    <row r="162" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>80</v>
       </c>
@@ -18915,7 +18920,7 @@
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
     </row>
-    <row r="163" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>80.5</v>
       </c>
@@ -18932,7 +18937,7 @@
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
     </row>
-    <row r="164" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>81</v>
       </c>
@@ -18949,7 +18954,7 @@
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
     </row>
-    <row r="165" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>81.5</v>
       </c>
@@ -18966,7 +18971,7 @@
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
     </row>
-    <row r="166" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>82</v>
       </c>
@@ -18983,7 +18988,7 @@
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
     </row>
-    <row r="167" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>82.5</v>
       </c>
@@ -19000,7 +19005,7 @@
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
     </row>
-    <row r="168" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>83</v>
       </c>
@@ -19017,7 +19022,7 @@
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
     </row>
-    <row r="169" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>83.5</v>
       </c>
@@ -19034,7 +19039,7 @@
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
     </row>
-    <row r="170" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>84</v>
       </c>
@@ -19051,7 +19056,7 @@
       <c r="F170" s="1"/>
       <c r="G170" s="1"/>
     </row>
-    <row r="171" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>84.5</v>
       </c>
@@ -19068,7 +19073,7 @@
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
     </row>
-    <row r="172" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>85</v>
       </c>
@@ -19085,7 +19090,7 @@
       <c r="F172" s="1"/>
       <c r="G172" s="1"/>
     </row>
-    <row r="173" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>85.5</v>
       </c>
@@ -19102,7 +19107,7 @@
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
     </row>
-    <row r="174" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>86</v>
       </c>
@@ -19119,7 +19124,7 @@
       <c r="F174" s="1"/>
       <c r="G174" s="1"/>
     </row>
-    <row r="175" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>86.5</v>
       </c>
@@ -19136,7 +19141,7 @@
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
     </row>
-    <row r="176" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>87</v>
       </c>
@@ -19153,7 +19158,7 @@
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
     </row>
-    <row r="177" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>87.5</v>
       </c>
@@ -19170,7 +19175,7 @@
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
     </row>
-    <row r="178" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>88</v>
       </c>
@@ -19187,7 +19192,7 @@
       <c r="F178" s="1"/>
       <c r="G178" s="1"/>
     </row>
-    <row r="179" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>88.5</v>
       </c>
@@ -19204,7 +19209,7 @@
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
     </row>
-    <row r="180" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>89</v>
       </c>
@@ -19221,7 +19226,7 @@
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
     </row>
-    <row r="181" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>89.5</v>
       </c>
@@ -19238,7 +19243,7 @@
       <c r="F181" s="1"/>
       <c r="G181" s="1"/>
     </row>
-    <row r="182" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>90</v>
       </c>
@@ -19255,7 +19260,7 @@
       <c r="F182" s="1"/>
       <c r="G182" s="1"/>
     </row>
-    <row r="183" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>90.5</v>
       </c>
@@ -19272,7 +19277,7 @@
       <c r="F183" s="1"/>
       <c r="G183" s="1"/>
     </row>
-    <row r="184" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>91</v>
       </c>
@@ -19289,7 +19294,7 @@
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
     </row>
-    <row r="185" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>91.5</v>
       </c>
@@ -19306,7 +19311,7 @@
       <c r="F185" s="1"/>
       <c r="G185" s="1"/>
     </row>
-    <row r="186" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>92</v>
       </c>
@@ -19323,7 +19328,7 @@
       <c r="F186" s="1"/>
       <c r="G186" s="1"/>
     </row>
-    <row r="187" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>92.5</v>
       </c>
@@ -19340,7 +19345,7 @@
       <c r="F187" s="1"/>
       <c r="G187" s="1"/>
     </row>
-    <row r="188" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>93</v>
       </c>
@@ -19357,7 +19362,7 @@
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
     </row>
-    <row r="189" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>93.5</v>
       </c>
@@ -19374,7 +19379,7 @@
       <c r="F189" s="1"/>
       <c r="G189" s="1"/>
     </row>
-    <row r="190" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>94</v>
       </c>
@@ -19391,7 +19396,7 @@
       <c r="F190" s="1"/>
       <c r="G190" s="1"/>
     </row>
-    <row r="191" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>94.5</v>
       </c>
@@ -19408,7 +19413,7 @@
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
     </row>
-    <row r="192" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>95</v>
       </c>
@@ -19425,7 +19430,7 @@
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
     </row>
-    <row r="193" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>95.5</v>
       </c>
@@ -19442,7 +19447,7 @@
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
     </row>
-    <row r="194" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>96</v>
       </c>
@@ -19459,7 +19464,7 @@
       <c r="F194" s="1"/>
       <c r="G194" s="1"/>
     </row>
-    <row r="195" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>96.5</v>
       </c>
@@ -19476,7 +19481,7 @@
       <c r="F195" s="1"/>
       <c r="G195" s="1"/>
     </row>
-    <row r="196" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>97</v>
       </c>
@@ -19493,7 +19498,7 @@
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
     </row>
-    <row r="197" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>97.5</v>
       </c>
@@ -19510,7 +19515,7 @@
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
     </row>
-    <row r="198" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>98</v>
       </c>
@@ -19527,7 +19532,7 @@
       <c r="F198" s="1"/>
       <c r="G198" s="1"/>
     </row>
-    <row r="199" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>98.5</v>
       </c>
@@ -19544,7 +19549,7 @@
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
     </row>
-    <row r="200" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>99</v>
       </c>
@@ -19561,7 +19566,7 @@
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
     </row>
-    <row r="201" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>99.5</v>
       </c>
@@ -19578,7 +19583,7 @@
       <c r="F201" s="1"/>
       <c r="G201" s="1"/>
     </row>
-    <row r="202" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>100</v>
       </c>
@@ -19616,7 +19621,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>100.5</v>
       </c>
@@ -19633,7 +19638,7 @@
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
     </row>
-    <row r="204" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>101</v>
       </c>
@@ -19650,7 +19655,7 @@
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
     </row>
-    <row r="205" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>101.5</v>
       </c>
@@ -19667,7 +19672,7 @@
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
     </row>
-    <row r="206" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>102</v>
       </c>
@@ -19684,7 +19689,7 @@
       <c r="F206" s="1"/>
       <c r="G206" s="1"/>
     </row>
-    <row r="207" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>102.5</v>
       </c>
@@ -19701,7 +19706,7 @@
       <c r="F207" s="1"/>
       <c r="G207" s="1"/>
     </row>
-    <row r="208" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>103</v>
       </c>
@@ -19718,7 +19723,7 @@
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
     </row>
-    <row r="209" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>103.5</v>
       </c>
@@ -19735,7 +19740,7 @@
       <c r="F209" s="1"/>
       <c r="G209" s="1"/>
     </row>
-    <row r="210" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>104</v>
       </c>
@@ -19752,7 +19757,7 @@
       <c r="F210" s="1"/>
       <c r="G210" s="1"/>
     </row>
-    <row r="211" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>104.5</v>
       </c>
@@ -19769,7 +19774,7 @@
       <c r="F211" s="1"/>
       <c r="G211" s="1"/>
     </row>
-    <row r="212" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>105</v>
       </c>
@@ -19786,7 +19791,7 @@
       <c r="F212" s="1"/>
       <c r="G212" s="1"/>
     </row>
-    <row r="213" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>105.5</v>
       </c>
@@ -19803,7 +19808,7 @@
       <c r="F213" s="1"/>
       <c r="G213" s="1"/>
     </row>
-    <row r="214" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>106</v>
       </c>
@@ -19820,7 +19825,7 @@
       <c r="F214" s="1"/>
       <c r="G214" s="1"/>
     </row>
-    <row r="215" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>106.5</v>
       </c>
@@ -19837,7 +19842,7 @@
       <c r="F215" s="1"/>
       <c r="G215" s="1"/>
     </row>
-    <row r="216" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>107</v>
       </c>
@@ -19854,7 +19859,7 @@
       <c r="F216" s="1"/>
       <c r="G216" s="1"/>
     </row>
-    <row r="217" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>107.5</v>
       </c>
@@ -19871,7 +19876,7 @@
       <c r="F217" s="1"/>
       <c r="G217" s="1"/>
     </row>
-    <row r="218" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>108</v>
       </c>
@@ -19888,7 +19893,7 @@
       <c r="F218" s="1"/>
       <c r="G218" s="1"/>
     </row>
-    <row r="219" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>108.5</v>
       </c>
@@ -19905,7 +19910,7 @@
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
     </row>
-    <row r="220" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>109</v>
       </c>
@@ -19922,7 +19927,7 @@
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
     </row>
-    <row r="221" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>109.5</v>
       </c>
@@ -19939,7 +19944,7 @@
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
     </row>
-    <row r="222" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>110</v>
       </c>
@@ -19956,7 +19961,7 @@
       <c r="F222" s="1"/>
       <c r="G222" s="1"/>
     </row>
-    <row r="223" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>110.5</v>
       </c>
@@ -19973,7 +19978,7 @@
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
     </row>
-    <row r="224" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>111</v>
       </c>
@@ -19990,7 +19995,7 @@
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
     </row>
-    <row r="225" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>111.5</v>
       </c>
@@ -20007,7 +20012,7 @@
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
     </row>
-    <row r="226" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>112</v>
       </c>
@@ -20024,7 +20029,7 @@
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
     </row>
-    <row r="227" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>112.5</v>
       </c>
@@ -20041,7 +20046,7 @@
       <c r="F227" s="1"/>
       <c r="G227" s="1"/>
     </row>
-    <row r="228" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>113</v>
       </c>
@@ -20058,7 +20063,7 @@
       <c r="F228" s="1"/>
       <c r="G228" s="1"/>
     </row>
-    <row r="229" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>113.5</v>
       </c>
@@ -20075,7 +20080,7 @@
       <c r="F229" s="1"/>
       <c r="G229" s="1"/>
     </row>
-    <row r="230" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>114</v>
       </c>
@@ -20092,7 +20097,7 @@
       <c r="F230" s="1"/>
       <c r="G230" s="1"/>
     </row>
-    <row r="231" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>114.5</v>
       </c>
@@ -20109,7 +20114,7 @@
       <c r="F231" s="1"/>
       <c r="G231" s="1"/>
     </row>
-    <row r="232" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>115</v>
       </c>
@@ -20126,7 +20131,7 @@
       <c r="F232" s="1"/>
       <c r="G232" s="1"/>
     </row>
-    <row r="233" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>115.5</v>
       </c>
@@ -20143,7 +20148,7 @@
       <c r="F233" s="1"/>
       <c r="G233" s="1"/>
     </row>
-    <row r="234" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>116</v>
       </c>
@@ -20160,7 +20165,7 @@
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
     </row>
-    <row r="235" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>116.5</v>
       </c>
@@ -20177,7 +20182,7 @@
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
     </row>
-    <row r="236" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>117</v>
       </c>
@@ -20194,7 +20199,7 @@
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
     </row>
-    <row r="237" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>117.5</v>
       </c>
@@ -20211,7 +20216,7 @@
       <c r="F237" s="1"/>
       <c r="G237" s="1"/>
     </row>
-    <row r="238" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>118</v>
       </c>
@@ -20228,7 +20233,7 @@
       <c r="F238" s="1"/>
       <c r="G238" s="1"/>
     </row>
-    <row r="239" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>118.5</v>
       </c>
@@ -20245,7 +20250,7 @@
       <c r="F239" s="1"/>
       <c r="G239" s="1"/>
     </row>
-    <row r="240" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>119</v>
       </c>
@@ -20262,7 +20267,7 @@
       <c r="F240" s="1"/>
       <c r="G240" s="1"/>
     </row>
-    <row r="241" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>119.5</v>
       </c>
@@ -20279,7 +20284,7 @@
       <c r="F241" s="1"/>
       <c r="G241" s="1"/>
     </row>
-    <row r="242" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>120</v>
       </c>
